--- a/task167/golden/call_reserve_2027.xlsx
+++ b/task167/golden/call_reserve_2027.xlsx
@@ -82,7 +82,7 @@
     <t>Year of age</t>
   </si>
   <si>
-    <t>First year fees and expenses only</t>
+    <t>Light first year (under 8 per cent)</t>
   </si>
   <si>
     <t>Funds</t>
@@ -94,7 +94,7 @@
     <t>All funds</t>
   </si>
   <si>
-    <t>Second-year calls, left out one vintage at a time: the funds whose first year was fees and expenses only, $ million</t>
+    <t>Second-year calls, left out one vintage at a time: the funds with a light first year, $ million</t>
   </si>
   <si>
     <t>Vintage</t>
@@ -142,10 +142,10 @@
     <t>Expected 2027 calls ($m)</t>
   </si>
   <si>
-    <t>BF-0116</t>
-  </si>
-  <si>
-    <t>Ravmere Ventures Fund II</t>
+    <t>BF-0142</t>
+  </si>
+  <si>
+    <t>Mardale Ventures Fund II</t>
   </si>
   <si>
     <t>Venture capital</t>
@@ -154,13 +154,7 @@
     <t>USD</t>
   </si>
   <si>
-    <t>investments</t>
-  </si>
-  <si>
-    <t>BF-0129</t>
-  </si>
-  <si>
-    <t>Pelbury Fund III</t>
+    <t>light</t>
   </si>
   <si>
     <t>BF-0151</t>
@@ -172,12 +166,27 @@
     <t>Growth equity</t>
   </si>
   <si>
+    <t>ordinary</t>
+  </si>
+  <si>
     <t>BF-0155</t>
   </si>
   <si>
     <t>Talwick Fund II</t>
   </si>
   <si>
+    <t>BF-0157</t>
+  </si>
+  <si>
+    <t>Rosgate Ventures Fund IV</t>
+  </si>
+  <si>
+    <t>BF-0161</t>
+  </si>
+  <si>
+    <t>Holvane Fund I</t>
+  </si>
+  <si>
     <t>BF-0164</t>
   </si>
   <si>
@@ -190,6 +199,15 @@
     <t>Lormere Ventures Fund IV</t>
   </si>
   <si>
+    <t>BF-0175</t>
+  </si>
+  <si>
+    <t>Dalmere Capital Partners II</t>
+  </si>
+  <si>
+    <t>Buyout</t>
+  </si>
+  <si>
     <t>BF-0177</t>
   </si>
   <si>
@@ -202,9 +220,6 @@
     <t>Lormoor Partners III</t>
   </si>
   <si>
-    <t>Buyout</t>
-  </si>
-  <si>
     <t>EUR</t>
   </si>
   <si>
@@ -220,10 +235,10 @@
     <t>Aldmoor Fund II</t>
   </si>
   <si>
-    <t>BF-0191</t>
-  </si>
-  <si>
-    <t>Dalbrook Growth Fund IV</t>
+    <t>BF-0189</t>
+  </si>
+  <si>
+    <t>Belwick Fund II</t>
   </si>
   <si>
     <t>BF-0192</t>
@@ -232,12 +247,6 @@
     <t>Ravmere Ventures Fund III</t>
   </si>
   <si>
-    <t>BF-0197</t>
-  </si>
-  <si>
-    <t>Selley Fund III</t>
-  </si>
-  <si>
     <t>BF-0200</t>
   </si>
   <si>
@@ -256,12 +265,6 @@
     <t>Corwick Fund III</t>
   </si>
   <si>
-    <t>BF-0207</t>
-  </si>
-  <si>
-    <t>Halgate Fund V</t>
-  </si>
-  <si>
     <t>BF-0208</t>
   </si>
   <si>
@@ -328,9 +331,6 @@
     <t>Dalcrest Fund III</t>
   </si>
   <si>
-    <t>fees and expenses only</t>
-  </si>
-  <si>
     <t>BF-0235</t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>Value 31 Dec 2026 ($m)</t>
   </si>
   <si>
-    <t>Reported NAV, contributions and distributions in the fund's currency, from the administrator's capital account summary and the notices after each NAV date; a reported NAV below zero is the general partner's figure for a fund whose first deals sit on its credit line.</t>
+    <t>Reported NAV, contributions and distributions in the fund's currency, from the administrator's capital account summary and the notices after each NAV date.</t>
   </si>
   <si>
     <t>Reserve account 6011-2207, qualifying assets at 31 December 2026</t>
@@ -1605,7 +1605,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>210.6</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1613,7 +1613,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>239.4</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1684,19 +1684,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="7">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="C5">
         <v>36</v>
       </c>
       <c r="D5" s="7">
-        <v>33</v>
+        <v>31.8</v>
       </c>
       <c r="E5">
         <v>136</v>
       </c>
       <c r="F5" s="7">
-        <v>26.1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,19 +1704,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="7">
-        <v>43.3</v>
+        <v>37.3</v>
       </c>
       <c r="C6">
         <v>36</v>
       </c>
       <c r="D6" s="7">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="E6">
         <v>136</v>
       </c>
       <c r="F6" s="7">
-        <v>23.3</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,19 +1724,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="7">
-        <v>14.8</v>
+        <v>16.6</v>
       </c>
       <c r="C7">
         <v>36</v>
       </c>
       <c r="D7" s="7">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="E7">
         <v>136</v>
       </c>
       <c r="F7" s="7">
-        <v>15</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1744,13 +1744,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="7">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="C8">
         <v>36</v>
       </c>
       <c r="D8" s="7">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="E8">
         <v>136</v>
@@ -1764,19 +1764,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="7">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C9">
         <v>35</v>
       </c>
       <c r="D9" s="7">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="E9">
         <v>126</v>
       </c>
       <c r="F9" s="7">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,19 +1784,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="7">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="C10">
         <v>31</v>
       </c>
       <c r="D10" s="7">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="E10">
         <v>118</v>
       </c>
       <c r="F10" s="7">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1804,19 +1804,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="7">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>26</v>
       </c>
       <c r="D11" s="7">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="E11">
         <v>111</v>
       </c>
       <c r="F11" s="7">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1824,19 +1824,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>24</v>
       </c>
       <c r="D12" s="7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E12">
         <v>102</v>
       </c>
       <c r="F12" s="7">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1850,13 +1850,13 @@
         <v>20</v>
       </c>
       <c r="D13" s="7">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E13">
         <v>93</v>
       </c>
       <c r="F13" s="7">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1864,13 +1864,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="7">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C14">
         <v>17</v>
       </c>
       <c r="D14" s="7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E14">
         <v>84</v>
@@ -1909,13 +1909,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="5">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="D18" s="5">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="E18" s="5">
-        <v>11</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1926,13 +1926,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="5">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="D19" s="5">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="E19" s="5">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1943,13 +1943,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="5">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="D20" s="5">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="E20" s="5">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1960,13 +1960,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="5">
-        <v>29.5</v>
+        <v>28</v>
       </c>
       <c r="D21" s="5">
-        <v>17.3</v>
+        <v>15.8</v>
       </c>
       <c r="E21" s="5">
-        <v>32.5</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1977,13 +1977,13 @@
         <v>4</v>
       </c>
       <c r="C22" s="5">
-        <v>58.6</v>
+        <v>46.3</v>
       </c>
       <c r="D22" s="5">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="E22" s="5">
-        <v>51</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1994,13 +1994,13 @@
         <v>6</v>
       </c>
       <c r="C23" s="5">
-        <v>71.2</v>
+        <v>63.7</v>
       </c>
       <c r="D23" s="5">
-        <v>42.5</v>
+        <v>38.6</v>
       </c>
       <c r="E23" s="5">
-        <v>81.90000000000001</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2011,13 +2011,13 @@
         <v>4</v>
       </c>
       <c r="C24" s="5">
-        <v>47.8</v>
+        <v>41.6</v>
       </c>
       <c r="D24" s="5">
-        <v>27.2</v>
+        <v>24.9</v>
       </c>
       <c r="E24" s="5">
-        <v>51.6</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2028,13 +2028,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="5">
-        <v>45.2</v>
+        <v>38.5</v>
       </c>
       <c r="D25" s="5">
-        <v>24.8</v>
+        <v>22.7</v>
       </c>
       <c r="E25" s="5">
-        <v>46.9</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2045,13 +2045,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="5">
-        <v>44.2</v>
+        <v>42.9</v>
       </c>
       <c r="D26" s="5">
-        <v>23</v>
+        <v>20.8</v>
       </c>
       <c r="E26" s="5">
-        <v>42.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2062,13 +2062,13 @@
         <v>4</v>
       </c>
       <c r="C27" s="5">
-        <v>48.8</v>
+        <v>43.3</v>
       </c>
       <c r="D27" s="5">
-        <v>26.3</v>
+        <v>24</v>
       </c>
       <c r="E27" s="5">
-        <v>49.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2079,13 +2079,13 @@
         <v>5</v>
       </c>
       <c r="C28" s="5">
-        <v>68.09999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="D28" s="5">
-        <v>36.4</v>
+        <v>33.2</v>
       </c>
       <c r="E28" s="5">
-        <v>68.8</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2096,13 +2096,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="5">
-        <v>22.5</v>
+        <v>15.8</v>
       </c>
       <c r="D29" s="5">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E29" s="5">
-        <v>17.4</v>
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>
@@ -2180,19 +2180,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E5" s="9">
-        <v>39095</v>
+        <v>39692</v>
       </c>
       <c r="F5" t="s">
         <v>41</v>
       </c>
       <c r="G5" s="10">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="H5" s="7">
-        <v>37.1</v>
+        <v>6.1</v>
       </c>
       <c r="I5" t="s">
         <v>42</v>
@@ -2209,25 +2209,25 @@
         <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="E6" s="9">
-        <v>39382</v>
+        <v>39879</v>
       </c>
       <c r="F6" t="s">
         <v>41</v>
       </c>
       <c r="G6" s="10">
-        <v>27.5</v>
+        <v>18.75</v>
       </c>
       <c r="H6" s="7">
-        <v>26.3</v>
+        <v>30.8</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -2235,31 +2235,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>2009</v>
       </c>
       <c r="E7" s="9">
-        <v>39879</v>
+        <v>40067</v>
       </c>
       <c r="F7" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="10">
-        <v>18.75</v>
+        <v>18.25</v>
       </c>
       <c r="H7" s="7">
-        <v>29.9</v>
+        <v>37.8</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
@@ -2279,19 +2279,19 @@
         <v>2009</v>
       </c>
       <c r="E8" s="9">
-        <v>40067</v>
+        <v>40078</v>
       </c>
       <c r="F8" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="10">
-        <v>18.25</v>
+        <v>29.5</v>
       </c>
       <c r="H8" s="7">
-        <v>37.9</v>
+        <v>29.6</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -2299,28 +2299,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E9" s="9">
-        <v>40214</v>
+        <v>40163</v>
       </c>
       <c r="F9" t="s">
         <v>41</v>
       </c>
       <c r="G9" s="10">
-        <v>17.75</v>
+        <v>30.5</v>
       </c>
       <c r="H9" s="7">
-        <v>30.8</v>
+        <v>6.9</v>
       </c>
       <c r="I9" t="s">
         <v>42</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -2343,19 +2343,19 @@
         <v>2010</v>
       </c>
       <c r="E10" s="9">
-        <v>40347</v>
+        <v>40214</v>
       </c>
       <c r="F10" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="10">
-        <v>30</v>
+        <v>17.75</v>
       </c>
       <c r="H10" s="7">
-        <v>27.7</v>
+        <v>25.5</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J10" s="5">
         <v>0</v>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
         <v>40</v>
@@ -2375,19 +2375,19 @@
         <v>2010</v>
       </c>
       <c r="E11" s="9">
-        <v>40516</v>
+        <v>40347</v>
       </c>
       <c r="F11" t="s">
         <v>41</v>
       </c>
       <c r="G11" s="10">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="H11" s="7">
-        <v>34.4</v>
+        <v>31.6</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
@@ -2395,31 +2395,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E12" s="9">
-        <v>40565</v>
+        <v>40400</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="G12" s="10">
-        <v>22.25</v>
+        <v>19.5</v>
       </c>
       <c r="H12" s="7">
-        <v>23.4</v>
+        <v>36.6</v>
       </c>
       <c r="I12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J12" s="5">
         <v>0</v>
@@ -2436,22 +2436,22 @@
         <v>40</v>
       </c>
       <c r="D13">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E13" s="9">
-        <v>40565</v>
+        <v>40516</v>
       </c>
       <c r="F13" t="s">
         <v>41</v>
       </c>
       <c r="G13" s="10">
-        <v>18.75</v>
+        <v>19.5</v>
       </c>
       <c r="H13" s="7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J13" s="5">
         <v>0</v>
@@ -2465,25 +2465,25 @@
         <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14">
         <v>2011</v>
       </c>
       <c r="E14" s="9">
-        <v>40667</v>
+        <v>40565</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G14" s="10">
-        <v>26.25</v>
+        <v>22.25</v>
       </c>
       <c r="H14" s="7">
-        <v>40.4</v>
+        <v>30.2</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J14" s="5">
         <v>0</v>
@@ -2491,31 +2491,31 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>2011</v>
       </c>
       <c r="E15" s="9">
-        <v>40740</v>
+        <v>40565</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="G15" s="10">
-        <v>22.75</v>
+        <v>18.75</v>
       </c>
       <c r="H15" s="7">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J15" s="5">
         <v>0</v>
@@ -2523,31 +2523,31 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D16">
         <v>2011</v>
       </c>
       <c r="E16" s="9">
-        <v>40801</v>
+        <v>40667</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G16" s="10">
-        <v>28.5</v>
+        <v>26.25</v>
       </c>
       <c r="H16" s="7">
-        <v>36.2</v>
+        <v>29.2</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J16" s="5">
         <v>0</v>
@@ -2555,31 +2555,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D17">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E17" s="9">
-        <v>40978</v>
+        <v>40712</v>
       </c>
       <c r="F17" t="s">
         <v>41</v>
       </c>
       <c r="G17" s="10">
-        <v>22</v>
+        <v>31.75</v>
       </c>
       <c r="H17" s="7">
-        <v>40.2</v>
+        <v>43.6</v>
       </c>
       <c r="I17" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J17" s="5">
         <v>0</v>
@@ -2587,31 +2587,31 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
       </c>
       <c r="D18">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E18" s="9">
-        <v>40984</v>
+        <v>40801</v>
       </c>
       <c r="F18" t="s">
         <v>41</v>
       </c>
       <c r="G18" s="10">
-        <v>24.25</v>
+        <v>28.5</v>
       </c>
       <c r="H18" s="7">
-        <v>21.9</v>
+        <v>28.9</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J18" s="5">
         <v>0</v>
@@ -2619,31 +2619,31 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D19">
         <v>2012</v>
       </c>
       <c r="E19" s="9">
-        <v>41021</v>
+        <v>40984</v>
       </c>
       <c r="F19" t="s">
         <v>41</v>
       </c>
       <c r="G19" s="10">
-        <v>26.75</v>
+        <v>24.25</v>
       </c>
       <c r="H19" s="7">
-        <v>50.5</v>
+        <v>28.4</v>
       </c>
       <c r="I19" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J19" s="5">
         <v>0</v>
@@ -2651,31 +2651,31 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20">
         <v>2012</v>
       </c>
       <c r="E20" s="9">
-        <v>41046</v>
+        <v>41021</v>
       </c>
       <c r="F20" t="s">
         <v>41</v>
       </c>
       <c r="G20" s="10">
-        <v>28.5</v>
+        <v>26.75</v>
       </c>
       <c r="H20" s="7">
-        <v>36.2</v>
+        <v>32.2</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J20" s="5">
         <v>0</v>
@@ -2683,31 +2683,31 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21">
         <v>2012</v>
       </c>
       <c r="E21" s="9">
-        <v>41104</v>
+        <v>41046</v>
       </c>
       <c r="F21" t="s">
         <v>41</v>
       </c>
       <c r="G21" s="10">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="H21" s="7">
-        <v>34.9</v>
+        <v>36.4</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J21" s="5">
         <v>0</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
@@ -2736,10 +2736,10 @@
         <v>24.75</v>
       </c>
       <c r="H22" s="7">
-        <v>32.3</v>
+        <v>37.1</v>
       </c>
       <c r="I22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
@@ -2747,13 +2747,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <v>2012</v>
@@ -2768,10 +2768,10 @@
         <v>28.75</v>
       </c>
       <c r="H23" s="7">
-        <v>38.5</v>
+        <v>31.7</v>
       </c>
       <c r="I23" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J23" s="5">
         <v>0</v>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D24">
         <v>2013</v>
@@ -2800,10 +2800,10 @@
         <v>20.75</v>
       </c>
       <c r="H24" s="7">
-        <v>39.9</v>
+        <v>35.5</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J24" s="5">
         <v>0</v>
@@ -2811,13 +2811,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25">
         <v>2013</v>
@@ -2832,10 +2832,10 @@
         <v>32</v>
       </c>
       <c r="H25" s="7">
-        <v>38.8</v>
+        <v>31.2</v>
       </c>
       <c r="I25" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J25" s="5">
         <v>0</v>
@@ -2843,13 +2843,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D26">
         <v>2013</v>
@@ -2864,10 +2864,10 @@
         <v>30.75</v>
       </c>
       <c r="H26" s="7">
-        <v>36.4</v>
+        <v>31.6</v>
       </c>
       <c r="I26" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J26" s="5">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
@@ -2896,10 +2896,10 @@
         <v>23.25</v>
       </c>
       <c r="H27" s="7">
-        <v>33.6</v>
+        <v>29</v>
       </c>
       <c r="I27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J27" s="5">
         <v>0</v>
@@ -2907,13 +2907,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D28">
         <v>2013</v>
@@ -2928,10 +2928,10 @@
         <v>24.5</v>
       </c>
       <c r="H28" s="7">
-        <v>39</v>
+        <v>31.6</v>
       </c>
       <c r="I28" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J28" s="5">
         <v>0</v>
@@ -2939,13 +2939,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D29">
         <v>2013</v>
@@ -2960,10 +2960,10 @@
         <v>35.5</v>
       </c>
       <c r="H29" s="7">
-        <v>23.3</v>
+        <v>35.2</v>
       </c>
       <c r="I29" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J29" s="5">
         <v>0</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
@@ -2992,10 +2992,10 @@
         <v>35.75</v>
       </c>
       <c r="H30" s="7">
-        <v>24.7</v>
+        <v>12.6</v>
       </c>
       <c r="I30" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J30" s="5">
         <v>0</v>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D31">
         <v>2014</v>
@@ -3024,10 +3024,10 @@
         <v>20.25</v>
       </c>
       <c r="H31" s="7">
-        <v>39.9</v>
+        <v>17.8</v>
       </c>
       <c r="I31" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J31" s="5">
         <v>0</v>
@@ -3035,13 +3035,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32">
         <v>2014</v>
@@ -3056,10 +3056,10 @@
         <v>32.5</v>
       </c>
       <c r="H32" s="7">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="I32" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J32" s="5">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D33">
         <v>2014</v>
@@ -3088,10 +3088,10 @@
         <v>21.5</v>
       </c>
       <c r="H33" s="7">
-        <v>30.1</v>
+        <v>12.6</v>
       </c>
       <c r="I33" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J33" s="5">
         <v>0</v>
@@ -3120,10 +3120,10 @@
         <v>35.75</v>
       </c>
       <c r="H34" s="7">
-        <v>34.7</v>
+        <v>29.3</v>
       </c>
       <c r="I34" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J34" s="5">
         <v>0</v>
@@ -3137,7 +3137,7 @@
         <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D35">
         <v>2014</v>
@@ -3152,10 +3152,10 @@
         <v>20.5</v>
       </c>
       <c r="H35" s="7">
-        <v>27.2</v>
+        <v>37.6</v>
       </c>
       <c r="I35" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J35" s="5">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D36">
         <v>2014</v>
@@ -3178,16 +3178,16 @@
         <v>41785</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G36" s="10">
         <v>25</v>
       </c>
       <c r="H36" s="7">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="I36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J36" s="5">
         <v>0</v>
@@ -3216,10 +3216,10 @@
         <v>20.25</v>
       </c>
       <c r="H37" s="7">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="I37" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J37" s="5">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D38">
         <v>2014</v>
@@ -3248,10 +3248,10 @@
         <v>21.75</v>
       </c>
       <c r="H38" s="7">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="I38" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J38" s="5">
         <v>0</v>
@@ -3265,7 +3265,7 @@
         <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D39">
         <v>2014</v>
@@ -3274,16 +3274,16 @@
         <v>41931</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G39" s="10">
         <v>22.75</v>
       </c>
       <c r="H39" s="7">
-        <v>29.6</v>
+        <v>29.3</v>
       </c>
       <c r="I39" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J39" s="5">
         <v>0</v>
@@ -3297,7 +3297,7 @@
         <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D40">
         <v>2014</v>
@@ -3306,16 +3306,16 @@
         <v>41976</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G40" s="10">
         <v>17.25</v>
       </c>
       <c r="H40" s="7">
-        <v>28</v>
+        <v>30.4</v>
       </c>
       <c r="I40" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J40" s="5">
         <v>0</v>
@@ -3344,10 +3344,10 @@
         <v>28.25</v>
       </c>
       <c r="H41" s="7">
-        <v>33.8</v>
+        <v>39.5</v>
       </c>
       <c r="I41" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J41" s="5">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D42">
         <v>2015</v>
@@ -3376,10 +3376,10 @@
         <v>25.75</v>
       </c>
       <c r="H42" s="7">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="I42" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J42" s="5">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D43">
         <v>2015</v>
@@ -3408,10 +3408,10 @@
         <v>30</v>
       </c>
       <c r="H43" s="7">
-        <v>34.1</v>
+        <v>33</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J43" s="5">
         <v>0</v>
@@ -3440,10 +3440,10 @@
         <v>21.5</v>
       </c>
       <c r="H44" s="7">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="I44" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J44" s="5">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D45">
         <v>2015</v>
@@ -3472,10 +3472,10 @@
         <v>26.25</v>
       </c>
       <c r="H45" s="7">
-        <v>35.6</v>
+        <v>33.5</v>
       </c>
       <c r="I45" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J45" s="5">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D46">
         <v>2015</v>
@@ -3504,13 +3504,13 @@
         <v>37.25</v>
       </c>
       <c r="H46" s="7">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="I46" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J46" s="5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -3536,10 +3536,10 @@
         <v>37.25</v>
       </c>
       <c r="H47" s="7">
-        <v>18.3</v>
+        <v>32.5</v>
       </c>
       <c r="I47" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J47" s="5">
         <v>0</v>
@@ -3568,13 +3568,13 @@
         <v>27</v>
       </c>
       <c r="H48" s="7">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="I48" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J48" s="5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -3600,13 +3600,13 @@
         <v>33.75</v>
       </c>
       <c r="H49" s="7">
-        <v>30.1</v>
+        <v>31.2</v>
       </c>
       <c r="I49" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J49" s="5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -3617,7 +3617,7 @@
         <v>136</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D50">
         <v>2015</v>
@@ -3632,10 +3632,10 @@
         <v>35.5</v>
       </c>
       <c r="H50" s="7">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="I50" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J50" s="5">
         <v>0.1</v>
@@ -3664,10 +3664,10 @@
         <v>28.5</v>
       </c>
       <c r="H51" s="7">
-        <v>27.6</v>
+        <v>32.7</v>
       </c>
       <c r="I51" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J51" s="5">
         <v>0.1</v>
@@ -3696,13 +3696,13 @@
         <v>33.75</v>
       </c>
       <c r="H52" s="7">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="I52" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J52" s="5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -3728,10 +3728,10 @@
         <v>38</v>
       </c>
       <c r="H53" s="7">
-        <v>51.2</v>
+        <v>35.6</v>
       </c>
       <c r="I53" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J53" s="5">
         <v>0.1</v>
@@ -3760,10 +3760,10 @@
         <v>35.25</v>
       </c>
       <c r="H54" s="7">
-        <v>45.7</v>
+        <v>31.9</v>
       </c>
       <c r="I54" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J54" s="5">
         <v>0.1</v>
@@ -3777,7 +3777,7 @@
         <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D55">
         <v>2016</v>
@@ -3786,19 +3786,19 @@
         <v>42407</v>
       </c>
       <c r="F55" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G55" s="10">
         <v>19.25</v>
       </c>
       <c r="H55" s="7">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="I55" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J55" s="5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -3824,10 +3824,10 @@
         <v>22.75</v>
       </c>
       <c r="H56" s="7">
-        <v>35.6</v>
+        <v>32.3</v>
       </c>
       <c r="I56" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J56" s="5">
         <v>0.1</v>
@@ -3841,7 +3841,7 @@
         <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D57">
         <v>2016</v>
@@ -3856,13 +3856,13 @@
         <v>30</v>
       </c>
       <c r="H57" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I57" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J57" s="5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -3873,7 +3873,7 @@
         <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D58">
         <v>2016</v>
@@ -3888,10 +3888,10 @@
         <v>29.25</v>
       </c>
       <c r="H58" s="7">
-        <v>40.5</v>
+        <v>36.5</v>
       </c>
       <c r="I58" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J58" s="5">
         <v>0.1</v>
@@ -3905,7 +3905,7 @@
         <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D59">
         <v>2016</v>
@@ -3920,10 +3920,10 @@
         <v>36.25</v>
       </c>
       <c r="H59" s="7">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="I59" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J59" s="5">
         <v>0.1</v>
@@ -3946,16 +3946,16 @@
         <v>42545</v>
       </c>
       <c r="F60" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G60" s="10">
         <v>21</v>
       </c>
       <c r="H60" s="7">
-        <v>29.5</v>
+        <v>38</v>
       </c>
       <c r="I60" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J60" s="5">
         <v>0.1</v>
@@ -3984,10 +3984,10 @@
         <v>35.25</v>
       </c>
       <c r="H61" s="7">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="I61" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J61" s="5">
         <v>0.1</v>
@@ -4001,7 +4001,7 @@
         <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D62">
         <v>2016</v>
@@ -4016,13 +4016,13 @@
         <v>38.25</v>
       </c>
       <c r="H62" s="7">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="I62" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J62" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -4033,7 +4033,7 @@
         <v>163</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D63">
         <v>2016</v>
@@ -4042,19 +4042,19 @@
         <v>42623</v>
       </c>
       <c r="F63" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G63" s="10">
         <v>25.75</v>
       </c>
       <c r="H63" s="7">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="I63" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J63" s="5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>165</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D64">
         <v>2016</v>
@@ -4080,10 +4080,10 @@
         <v>39.75</v>
       </c>
       <c r="H64" s="7">
-        <v>29.7</v>
+        <v>46.2</v>
       </c>
       <c r="I64" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J64" s="5">
         <v>0.1</v>
@@ -4112,10 +4112,10 @@
         <v>31.75</v>
       </c>
       <c r="H65" s="7">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="I65" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J65" s="5">
         <v>0.1</v>
@@ -4144,13 +4144,13 @@
         <v>35.75</v>
       </c>
       <c r="H66" s="7">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="I66" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J66" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -4170,19 +4170,19 @@
         <v>42819</v>
       </c>
       <c r="F67" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G67" s="10">
         <v>23</v>
       </c>
       <c r="H67" s="7">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="I67" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J67" s="5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -4193,7 +4193,7 @@
         <v>173</v>
       </c>
       <c r="C68" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D68">
         <v>2017</v>
@@ -4202,16 +4202,16 @@
         <v>42821</v>
       </c>
       <c r="F68" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G68" s="10">
         <v>35.5</v>
       </c>
       <c r="H68" s="7">
-        <v>28.8</v>
+        <v>14.7</v>
       </c>
       <c r="I68" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J68" s="5">
         <v>0.1</v>
@@ -4225,7 +4225,7 @@
         <v>175</v>
       </c>
       <c r="C69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D69">
         <v>2017</v>
@@ -4240,10 +4240,10 @@
         <v>23</v>
       </c>
       <c r="H69" s="7">
-        <v>33</v>
+        <v>14.5</v>
       </c>
       <c r="I69" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J69" s="5">
         <v>0.1</v>
@@ -4257,7 +4257,7 @@
         <v>177</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D70">
         <v>2017</v>
@@ -4272,10 +4272,10 @@
         <v>27.5</v>
       </c>
       <c r="H70" s="7">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="I70" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J70" s="5">
         <v>0.1</v>
@@ -4304,10 +4304,10 @@
         <v>23.75</v>
       </c>
       <c r="H71" s="7">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J71" s="5">
         <v>0.1</v>
@@ -4321,7 +4321,7 @@
         <v>181</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D72">
         <v>2017</v>
@@ -4330,19 +4330,19 @@
         <v>42965</v>
       </c>
       <c r="F72" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G72" s="10">
         <v>30.75</v>
       </c>
       <c r="H72" s="7">
-        <v>42.9</v>
+        <v>40.3</v>
       </c>
       <c r="I72" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J72" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -4353,7 +4353,7 @@
         <v>183</v>
       </c>
       <c r="C73" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D73">
         <v>2017</v>
@@ -4368,10 +4368,10 @@
         <v>25</v>
       </c>
       <c r="H73" s="7">
-        <v>33.4</v>
+        <v>44.1</v>
       </c>
       <c r="I73" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J73" s="5">
         <v>0.1</v>
@@ -4385,7 +4385,7 @@
         <v>185</v>
       </c>
       <c r="C74" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D74">
         <v>2017</v>
@@ -4400,13 +4400,13 @@
         <v>33.25</v>
       </c>
       <c r="H74" s="7">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="I74" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J74" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -4432,10 +4432,10 @@
         <v>40.5</v>
       </c>
       <c r="H75" s="7">
-        <v>34</v>
+        <v>33.3</v>
       </c>
       <c r="I75" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J75" s="5">
         <v>0.2</v>
@@ -4464,10 +4464,10 @@
         <v>25.5</v>
       </c>
       <c r="H76" s="7">
-        <v>33.3</v>
+        <v>34.6</v>
       </c>
       <c r="I76" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J76" s="5">
         <v>0.1</v>
@@ -4481,7 +4481,7 @@
         <v>191</v>
       </c>
       <c r="C77" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D77">
         <v>2018</v>
@@ -4496,13 +4496,13 @@
         <v>42.5</v>
       </c>
       <c r="H77" s="7">
-        <v>27.5</v>
+        <v>36.4</v>
       </c>
       <c r="I77" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J77" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -4528,10 +4528,10 @@
         <v>23.75</v>
       </c>
       <c r="H78" s="7">
-        <v>2.5</v>
+        <v>7.3</v>
       </c>
       <c r="I78" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J78" s="5">
         <v>0.2</v>
@@ -4545,7 +4545,7 @@
         <v>195</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D79">
         <v>2018</v>
@@ -4560,10 +4560,10 @@
         <v>41.5</v>
       </c>
       <c r="H79" s="7">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="I79" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J79" s="5">
         <v>0.3</v>
@@ -4586,16 +4586,16 @@
         <v>43206</v>
       </c>
       <c r="F80" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G80" s="10">
         <v>24.25</v>
       </c>
       <c r="H80" s="7">
-        <v>35.7</v>
+        <v>11.1</v>
       </c>
       <c r="I80" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J80" s="5">
         <v>0.2</v>
@@ -4609,7 +4609,7 @@
         <v>199</v>
       </c>
       <c r="C81" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D81">
         <v>2018</v>
@@ -4624,13 +4624,13 @@
         <v>26.5</v>
       </c>
       <c r="H81" s="7">
-        <v>32.6</v>
+        <v>37.2</v>
       </c>
       <c r="I81" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J81" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -4656,10 +4656,10 @@
         <v>36.75</v>
       </c>
       <c r="H82" s="7">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="I82" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J82" s="5">
         <v>0.2</v>
@@ -4673,7 +4673,7 @@
         <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D83">
         <v>2018</v>
@@ -4688,13 +4688,13 @@
         <v>39</v>
       </c>
       <c r="H83" s="7">
-        <v>39</v>
+        <v>41.8</v>
       </c>
       <c r="I83" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J83" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -4705,7 +4705,7 @@
         <v>205</v>
       </c>
       <c r="C84" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D84">
         <v>2018</v>
@@ -4720,10 +4720,10 @@
         <v>42.5</v>
       </c>
       <c r="H84" s="7">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="I84" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J84" s="5">
         <v>0.4</v>
@@ -4737,7 +4737,7 @@
         <v>207</v>
       </c>
       <c r="C85" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D85">
         <v>2018</v>
@@ -4746,16 +4746,16 @@
         <v>43384</v>
       </c>
       <c r="F85" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G85" s="10">
         <v>26.5</v>
       </c>
       <c r="H85" s="7">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="I85" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J85" s="5">
         <v>0.2</v>
@@ -4769,7 +4769,7 @@
         <v>209</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D86">
         <v>2018</v>
@@ -4784,10 +4784,10 @@
         <v>38.75</v>
       </c>
       <c r="H86" s="7">
-        <v>35.5</v>
+        <v>33.7</v>
       </c>
       <c r="I86" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J86" s="5">
         <v>0.3</v>
@@ -4801,7 +4801,7 @@
         <v>211</v>
       </c>
       <c r="C87" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D87">
         <v>2018</v>
@@ -4816,10 +4816,10 @@
         <v>29.5</v>
       </c>
       <c r="H87" s="7">
-        <v>25.6</v>
+        <v>30.4</v>
       </c>
       <c r="I87" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J87" s="5">
         <v>0.2</v>
@@ -4833,7 +4833,7 @@
         <v>213</v>
       </c>
       <c r="C88" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D88">
         <v>2018</v>
@@ -4848,13 +4848,13 @@
         <v>32.5</v>
       </c>
       <c r="H88" s="7">
-        <v>36.5</v>
+        <v>42.1</v>
       </c>
       <c r="I88" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J88" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -4865,7 +4865,7 @@
         <v>215</v>
       </c>
       <c r="C89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D89">
         <v>2019</v>
@@ -4880,10 +4880,10 @@
         <v>32.25</v>
       </c>
       <c r="H89" s="7">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="I89" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J89" s="5">
         <v>0.4</v>
@@ -4912,13 +4912,13 @@
         <v>30.25</v>
       </c>
       <c r="H90" s="7">
-        <v>37.1</v>
+        <v>16.2</v>
       </c>
       <c r="I90" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J90" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -4929,7 +4929,7 @@
         <v>219</v>
       </c>
       <c r="C91" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D91">
         <v>2019</v>
@@ -4944,13 +4944,13 @@
         <v>35.25</v>
       </c>
       <c r="H91" s="7">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="I91" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J91" s="5">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -4961,7 +4961,7 @@
         <v>221</v>
       </c>
       <c r="C92" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D92">
         <v>2019</v>
@@ -4976,10 +4976,10 @@
         <v>30.5</v>
       </c>
       <c r="H92" s="7">
-        <v>31.7</v>
+        <v>33</v>
       </c>
       <c r="I92" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J92" s="5">
         <v>0.3</v>
@@ -5008,10 +5008,10 @@
         <v>40.25</v>
       </c>
       <c r="H93" s="7">
-        <v>35.4</v>
+        <v>36.4</v>
       </c>
       <c r="I93" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J93" s="5">
         <v>0.4</v>
@@ -5025,7 +5025,7 @@
         <v>225</v>
       </c>
       <c r="C94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D94">
         <v>2019</v>
@@ -5040,10 +5040,10 @@
         <v>37.5</v>
       </c>
       <c r="H94" s="7">
-        <v>38.2</v>
+        <v>31.5</v>
       </c>
       <c r="I94" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J94" s="5">
         <v>0.4</v>
@@ -5057,7 +5057,7 @@
         <v>227</v>
       </c>
       <c r="C95" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D95">
         <v>2019</v>
@@ -5072,10 +5072,10 @@
         <v>31.5</v>
       </c>
       <c r="H95" s="7">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="I95" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J95" s="5">
         <v>0.5</v>
@@ -5089,7 +5089,7 @@
         <v>229</v>
       </c>
       <c r="C96" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D96">
         <v>2019</v>
@@ -5104,10 +5104,10 @@
         <v>40.75</v>
       </c>
       <c r="H96" s="7">
-        <v>20.1</v>
+        <v>24.5</v>
       </c>
       <c r="I96" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J96" s="5">
         <v>0.5</v>
@@ -5121,7 +5121,7 @@
         <v>231</v>
       </c>
       <c r="C97" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D97">
         <v>2019</v>
@@ -5136,10 +5136,10 @@
         <v>24.75</v>
       </c>
       <c r="H97" s="7">
-        <v>31.3</v>
+        <v>37.6</v>
       </c>
       <c r="I97" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J97" s="5">
         <v>0.3</v>
@@ -5153,7 +5153,7 @@
         <v>233</v>
       </c>
       <c r="C98" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D98">
         <v>2019</v>
@@ -5168,10 +5168,10 @@
         <v>26.75</v>
       </c>
       <c r="H98" s="7">
-        <v>23.8</v>
+        <v>32.5</v>
       </c>
       <c r="I98" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J98" s="5">
         <v>0.3</v>
@@ -5185,7 +5185,7 @@
         <v>235</v>
       </c>
       <c r="C99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D99">
         <v>2019</v>
@@ -5200,10 +5200,10 @@
         <v>33.25</v>
       </c>
       <c r="H99" s="7">
-        <v>45.7</v>
+        <v>29.5</v>
       </c>
       <c r="I99" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J99" s="5">
         <v>0.4</v>
@@ -5232,13 +5232,13 @@
         <v>39.75</v>
       </c>
       <c r="H100" s="7">
-        <v>24.8</v>
+        <v>29.7</v>
       </c>
       <c r="I100" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J100" s="5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -5264,10 +5264,10 @@
         <v>36</v>
       </c>
       <c r="H101" s="7">
-        <v>32.9</v>
+        <v>34.4</v>
       </c>
       <c r="I101" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J101" s="5">
         <v>0.5</v>
@@ -5296,13 +5296,13 @@
         <v>29.75</v>
       </c>
       <c r="H102" s="7">
-        <v>30.3</v>
+        <v>34</v>
       </c>
       <c r="I102" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J102" s="5">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -5328,10 +5328,10 @@
         <v>25.75</v>
       </c>
       <c r="H103" s="7">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="I103" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J103" s="5">
         <v>0.5</v>
@@ -5345,7 +5345,7 @@
         <v>245</v>
       </c>
       <c r="C104" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D104">
         <v>2020</v>
@@ -5360,10 +5360,10 @@
         <v>31</v>
       </c>
       <c r="H104" s="7">
-        <v>30.7</v>
+        <v>16.5</v>
       </c>
       <c r="I104" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J104" s="5">
         <v>0.5</v>
@@ -5392,10 +5392,10 @@
         <v>26</v>
       </c>
       <c r="H105" s="7">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="I105" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J105" s="5">
         <v>0.6</v>
@@ -5409,7 +5409,7 @@
         <v>249</v>
       </c>
       <c r="C106" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D106">
         <v>2020</v>
@@ -5424,13 +5424,13 @@
         <v>34.25</v>
       </c>
       <c r="H106" s="7">
-        <v>34.7</v>
+        <v>35.3</v>
       </c>
       <c r="I106" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J106" s="5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -5441,7 +5441,7 @@
         <v>251</v>
       </c>
       <c r="C107" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D107">
         <v>2020</v>
@@ -5456,10 +5456,10 @@
         <v>30.75</v>
       </c>
       <c r="H107" s="7">
-        <v>33.4</v>
+        <v>30.3</v>
       </c>
       <c r="I107" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J107" s="5">
         <v>0.5</v>
@@ -5488,13 +5488,13 @@
         <v>30</v>
       </c>
       <c r="H108" s="7">
-        <v>30.7</v>
+        <v>34.9</v>
       </c>
       <c r="I108" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J108" s="5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -5505,7 +5505,7 @@
         <v>255</v>
       </c>
       <c r="C109" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D109">
         <v>2020</v>
@@ -5520,13 +5520,13 @@
         <v>24.5</v>
       </c>
       <c r="H109" s="7">
-        <v>25.6</v>
+        <v>26.2</v>
       </c>
       <c r="I109" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J109" s="5">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -5537,7 +5537,7 @@
         <v>257</v>
       </c>
       <c r="C110" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D110">
         <v>2020</v>
@@ -5552,13 +5552,13 @@
         <v>38.25</v>
       </c>
       <c r="H110" s="7">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="I110" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J110" s="5">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -5569,7 +5569,7 @@
         <v>259</v>
       </c>
       <c r="C111" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D111">
         <v>2020</v>
@@ -5584,10 +5584,10 @@
         <v>24</v>
       </c>
       <c r="H111" s="7">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="I111" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J111" s="5">
         <v>0.6</v>
@@ -5601,7 +5601,7 @@
         <v>261</v>
       </c>
       <c r="C112" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D112">
         <v>2020</v>
@@ -5616,13 +5616,13 @@
         <v>26.75</v>
       </c>
       <c r="H112" s="7">
-        <v>26.1</v>
+        <v>41.1</v>
       </c>
       <c r="I112" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J112" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -5633,7 +5633,7 @@
         <v>263</v>
       </c>
       <c r="C113" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D113">
         <v>2021</v>
@@ -5642,19 +5642,19 @@
         <v>44204</v>
       </c>
       <c r="F113" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G113" s="10">
         <v>24.75</v>
       </c>
       <c r="H113" s="7">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="I113" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J113" s="5">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -5674,19 +5674,19 @@
         <v>44233</v>
       </c>
       <c r="F114" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G114" s="10">
         <v>27.75</v>
       </c>
       <c r="H114" s="7">
-        <v>48.5</v>
+        <v>55.8</v>
       </c>
       <c r="I114" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J114" s="5">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -5697,7 +5697,7 @@
         <v>267</v>
       </c>
       <c r="C115" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D115">
         <v>2021</v>
@@ -5712,13 +5712,13 @@
         <v>36.5</v>
       </c>
       <c r="H115" s="7">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="I115" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J115" s="5">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -5729,7 +5729,7 @@
         <v>269</v>
       </c>
       <c r="C116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D116">
         <v>2021</v>
@@ -5744,13 +5744,13 @@
         <v>34.5</v>
       </c>
       <c r="H116" s="7">
-        <v>28.1</v>
+        <v>35.8</v>
       </c>
       <c r="I116" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J116" s="5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -5761,7 +5761,7 @@
         <v>271</v>
       </c>
       <c r="C117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D117">
         <v>2021</v>
@@ -5776,13 +5776,13 @@
         <v>44.25</v>
       </c>
       <c r="H117" s="7">
-        <v>34.9</v>
+        <v>48.3</v>
       </c>
       <c r="I117" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J117" s="5">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -5808,13 +5808,13 @@
         <v>28.25</v>
       </c>
       <c r="H118" s="7">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="I118" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J118" s="5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -5834,19 +5834,19 @@
         <v>44318</v>
       </c>
       <c r="F119" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G119" s="10">
         <v>29.5</v>
       </c>
       <c r="H119" s="7">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="I119" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J119" s="5">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -5857,7 +5857,7 @@
         <v>277</v>
       </c>
       <c r="C120" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D120">
         <v>2021</v>
@@ -5866,19 +5866,19 @@
         <v>44386</v>
       </c>
       <c r="F120" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G120" s="10">
         <v>39.5</v>
       </c>
       <c r="H120" s="7">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="I120" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J120" s="5">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -5889,7 +5889,7 @@
         <v>279</v>
       </c>
       <c r="C121" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D121">
         <v>2021</v>
@@ -5904,13 +5904,13 @@
         <v>33.5</v>
       </c>
       <c r="H121" s="7">
-        <v>40.8</v>
+        <v>33.3</v>
       </c>
       <c r="I121" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J121" s="5">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -5921,7 +5921,7 @@
         <v>281</v>
       </c>
       <c r="C122" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D122">
         <v>2021</v>
@@ -5936,13 +5936,13 @@
         <v>25.5</v>
       </c>
       <c r="H122" s="7">
-        <v>32.2</v>
+        <v>35.3</v>
       </c>
       <c r="I122" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J122" s="5">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -5953,7 +5953,7 @@
         <v>283</v>
       </c>
       <c r="C123" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D123">
         <v>2021</v>
@@ -5968,13 +5968,13 @@
         <v>25.25</v>
       </c>
       <c r="H123" s="7">
-        <v>48.6</v>
+        <v>39</v>
       </c>
       <c r="I123" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J123" s="5">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -6000,13 +6000,13 @@
         <v>32.5</v>
       </c>
       <c r="H124" s="7">
-        <v>35.2</v>
+        <v>31.5</v>
       </c>
       <c r="I124" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J124" s="5">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -6017,7 +6017,7 @@
         <v>287</v>
       </c>
       <c r="C125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D125">
         <v>2022</v>
@@ -6032,13 +6032,13 @@
         <v>31.25</v>
       </c>
       <c r="H125" s="7">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="I125" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J125" s="5">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -6049,7 +6049,7 @@
         <v>289</v>
       </c>
       <c r="C126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D126">
         <v>2022</v>
@@ -6064,13 +6064,13 @@
         <v>29.75</v>
       </c>
       <c r="H126" s="7">
-        <v>27.2</v>
+        <v>32.8</v>
       </c>
       <c r="I126" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J126" s="5">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -6081,7 +6081,7 @@
         <v>291</v>
       </c>
       <c r="C127" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D127">
         <v>2022</v>
@@ -6090,19 +6090,19 @@
         <v>44608</v>
       </c>
       <c r="F127" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G127" s="10">
         <v>31</v>
       </c>
       <c r="H127" s="7">
-        <v>29</v>
+        <v>50.5</v>
       </c>
       <c r="I127" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J127" s="5">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -6113,7 +6113,7 @@
         <v>293</v>
       </c>
       <c r="C128" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D128">
         <v>2022</v>
@@ -6128,13 +6128,13 @@
         <v>34.25</v>
       </c>
       <c r="H128" s="7">
-        <v>36.9</v>
+        <v>31.5</v>
       </c>
       <c r="I128" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J128" s="5">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -6145,7 +6145,7 @@
         <v>295</v>
       </c>
       <c r="C129" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D129">
         <v>2022</v>
@@ -6160,13 +6160,13 @@
         <v>40.5</v>
       </c>
       <c r="H129" s="7">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="I129" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J129" s="5">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -6177,7 +6177,7 @@
         <v>297</v>
       </c>
       <c r="C130" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D130">
         <v>2022</v>
@@ -6192,13 +6192,13 @@
         <v>27.75</v>
       </c>
       <c r="H130" s="7">
-        <v>31</v>
+        <v>13.9</v>
       </c>
       <c r="I130" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J130" s="5">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -6224,13 +6224,13 @@
         <v>40.25</v>
       </c>
       <c r="H131" s="7">
-        <v>31.9</v>
+        <v>34.1</v>
       </c>
       <c r="I131" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J131" s="5">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -6256,13 +6256,13 @@
         <v>32.5</v>
       </c>
       <c r="H132" s="7">
-        <v>33.4</v>
+        <v>41.4</v>
       </c>
       <c r="I132" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J132" s="5">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -6288,13 +6288,13 @@
         <v>26.5</v>
       </c>
       <c r="H133" s="7">
-        <v>36.4</v>
+        <v>28.9</v>
       </c>
       <c r="I133" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J133" s="5">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -6320,13 +6320,13 @@
         <v>46.25</v>
       </c>
       <c r="H134" s="7">
-        <v>30.5</v>
+        <v>26.6</v>
       </c>
       <c r="I134" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J134" s="5">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -6352,10 +6352,10 @@
         <v>30</v>
       </c>
       <c r="H135" s="7">
-        <v>32.6</v>
+        <v>27.9</v>
       </c>
       <c r="I135" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J135" s="5">
         <v>1.9</v>
@@ -6378,19 +6378,19 @@
         <v>44848</v>
       </c>
       <c r="F136" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G136" s="10">
         <v>27</v>
       </c>
       <c r="H136" s="7">
-        <v>28.9</v>
+        <v>36.7</v>
       </c>
       <c r="I136" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J136" s="5">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -6413,16 +6413,16 @@
         <v>41</v>
       </c>
       <c r="G137" s="10">
-        <v>51</v>
+        <v>58.5</v>
       </c>
       <c r="H137" s="7">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="I137" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J137" s="5">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -6433,7 +6433,7 @@
         <v>313</v>
       </c>
       <c r="C138" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D138">
         <v>2026</v>
@@ -6445,16 +6445,16 @@
         <v>41</v>
       </c>
       <c r="G138" s="10">
-        <v>75.5</v>
+        <v>87</v>
       </c>
       <c r="H138" s="7">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="I138" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J138" s="5">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -6477,16 +6477,16 @@
         <v>41</v>
       </c>
       <c r="G139" s="10">
-        <v>78.5</v>
+        <v>90.5</v>
       </c>
       <c r="H139" s="7">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="I139" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J139" s="5">
-        <v>34</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -6497,7 +6497,7 @@
         <v>317</v>
       </c>
       <c r="C140" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D140">
         <v>2026</v>
@@ -6506,19 +6506,19 @@
         <v>46047</v>
       </c>
       <c r="F140" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G140" s="10">
-        <v>75.5</v>
+        <v>86.5</v>
       </c>
       <c r="H140" s="7">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="I140" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J140" s="5">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -6541,16 +6541,16 @@
         <v>41</v>
       </c>
       <c r="G141" s="10">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H141" s="7">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="I141" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J141" s="5">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -6561,7 +6561,7 @@
         <v>321</v>
       </c>
       <c r="C142" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D142">
         <v>2026</v>
@@ -6570,19 +6570,19 @@
         <v>46066</v>
       </c>
       <c r="F142" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G142" s="10">
-        <v>72.5</v>
+        <v>83.5</v>
       </c>
       <c r="H142" s="7">
-        <v>28.3</v>
+        <v>35.6</v>
       </c>
       <c r="I142" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J142" s="5">
-        <v>14.6</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -6593,7 +6593,7 @@
         <v>323</v>
       </c>
       <c r="C143" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D143">
         <v>2026</v>
@@ -6605,16 +6605,16 @@
         <v>41</v>
       </c>
       <c r="G143" s="10">
-        <v>73.5</v>
+        <v>85</v>
       </c>
       <c r="H143" s="7">
-        <v>2.1</v>
+        <v>6.3</v>
       </c>
       <c r="I143" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J143" s="5">
-        <v>30</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -6625,7 +6625,7 @@
         <v>325</v>
       </c>
       <c r="C144" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D144">
         <v>2026</v>
@@ -6637,16 +6637,16 @@
         <v>41</v>
       </c>
       <c r="G144" s="10">
-        <v>55.5</v>
+        <v>64</v>
       </c>
       <c r="H144" s="7">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="I144" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J144" s="5">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -6669,16 +6669,16 @@
         <v>41</v>
       </c>
       <c r="G145" s="10">
-        <v>65.5</v>
+        <v>75.5</v>
       </c>
       <c r="H145" s="7">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="I145" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J145" s="5">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -6689,7 +6689,7 @@
         <v>329</v>
       </c>
       <c r="C146" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D146">
         <v>2026</v>
@@ -6701,16 +6701,16 @@
         <v>41</v>
       </c>
       <c r="G146" s="10">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H146" s="7">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="I146" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J146" s="5">
-        <v>29.8</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -6721,7 +6721,7 @@
         <v>331</v>
       </c>
       <c r="C147" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D147">
         <v>2026</v>
@@ -6733,16 +6733,16 @@
         <v>41</v>
       </c>
       <c r="G147" s="10">
-        <v>79.5</v>
+        <v>91.5</v>
       </c>
       <c r="H147" s="7">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="I147" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J147" s="5">
-        <v>32.4</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -6765,16 +6765,16 @@
         <v>41</v>
       </c>
       <c r="G148" s="10">
-        <v>81.5</v>
+        <v>94</v>
       </c>
       <c r="H148" s="7">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="I148" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J148" s="5">
-        <v>30.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -6785,7 +6785,7 @@
         <v>335</v>
       </c>
       <c r="C149" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D149">
         <v>2026</v>
@@ -6797,16 +6797,16 @@
         <v>41</v>
       </c>
       <c r="G149" s="10">
-        <v>52.5</v>
+        <v>60.5</v>
       </c>
       <c r="H149" s="7">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="I149" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J149" s="5">
-        <v>19.7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -6817,7 +6817,7 @@
         <v>337</v>
       </c>
       <c r="C150" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D150">
         <v>2026</v>
@@ -6826,19 +6826,19 @@
         <v>46111</v>
       </c>
       <c r="F150" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G150" s="10">
-        <v>73.5</v>
+        <v>85</v>
       </c>
       <c r="H150" s="7">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="I150" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J150" s="5">
-        <v>31.2</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -6846,7 +6846,7 @@
         <v>21</v>
       </c>
       <c r="J151" s="11">
-        <v>425.5</v>
+        <v>425.3</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -6897,18 +6897,18 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="5">
-        <v>553.1</v>
+        <v>617.8</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" s="5">
-        <v>252.1</v>
+        <v>242.2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6916,7 +6916,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="5">
-        <v>492.1</v>
+        <v>508.1</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6924,7 +6924,7 @@
         <v>143</v>
       </c>
       <c r="B8" s="5">
-        <v>34.5</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6932,7 +6932,7 @@
         <v>342</v>
       </c>
       <c r="B9" s="5">
-        <v>175.8</v>
+        <v>185.7</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -6940,7 +6940,7 @@
         <v>343</v>
       </c>
       <c r="B10" s="5">
-        <v>1156</v>
+        <v>1225.6</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -6948,7 +6948,7 @@
         <v>344</v>
       </c>
       <c r="B11" s="5">
-        <v>328.4</v>
+        <v>326.4</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -6956,7 +6956,7 @@
         <v>345</v>
       </c>
       <c r="B12" s="5">
-        <v>933.3</v>
+        <v>960.2</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -6964,7 +6964,7 @@
         <v>346</v>
       </c>
       <c r="B13" s="5">
-        <v>1331.8</v>
+        <v>1411.2</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -7006,22 +7006,22 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F17" s="10">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G17" s="9">
         <v>46295</v>
@@ -7033,27 +7033,27 @@
         <v>0</v>
       </c>
       <c r="J17" s="5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18">
         <v>2011</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F18" s="10">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="G18" s="9">
         <v>46295</v>
@@ -7065,27 +7065,27 @@
         <v>0</v>
       </c>
       <c r="J18" s="5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E19" t="s">
         <v>41</v>
       </c>
       <c r="F19" s="10">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="G19" s="9">
         <v>46295</v>
@@ -7094,30 +7094,30 @@
         <v>0</v>
       </c>
       <c r="I19" s="10">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="J19" s="5">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F20" s="10">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G20" s="9">
         <v>46295</v>
@@ -7129,18 +7129,18 @@
         <v>0</v>
       </c>
       <c r="J20" s="5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21">
         <v>2012</v>
@@ -7149,7 +7149,7 @@
         <v>41</v>
       </c>
       <c r="F21" s="10">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="G21" s="9">
         <v>46295</v>
@@ -7161,27 +7161,27 @@
         <v>0</v>
       </c>
       <c r="J21" s="5">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E22" t="s">
         <v>41</v>
       </c>
       <c r="F22" s="10">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="G22" s="9">
         <v>46295</v>
@@ -7193,18 +7193,18 @@
         <v>0</v>
       </c>
       <c r="J22" s="5">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23">
         <v>2013</v>
@@ -7213,7 +7213,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="10">
-        <v>0.88</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="9">
         <v>46295</v>
@@ -7222,21 +7222,21 @@
         <v>0</v>
       </c>
       <c r="I23" s="10">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J23" s="5">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D24">
         <v>2013</v>
@@ -7245,7 +7245,7 @@
         <v>41</v>
       </c>
       <c r="F24" s="10">
-        <v>0.79</v>
+        <v>1.25</v>
       </c>
       <c r="G24" s="9">
         <v>46295</v>
@@ -7254,21 +7254,21 @@
         <v>0</v>
       </c>
       <c r="I24" s="10">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25">
         <v>2013</v>
@@ -7277,7 +7277,7 @@
         <v>41</v>
       </c>
       <c r="F25" s="10">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="G25" s="9">
         <v>46295</v>
@@ -7286,62 +7286,62 @@
         <v>0</v>
       </c>
       <c r="I25" s="10">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J25" s="5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D26">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F26" s="10">
-        <v>0.86</v>
+        <v>0.18</v>
       </c>
       <c r="G26" s="9">
         <v>46295</v>
       </c>
       <c r="H26" s="10">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I26" s="10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="5">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27">
         <v>2014</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F27" s="10">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="G27" s="9">
         <v>46295</v>
@@ -7350,21 +7350,21 @@
         <v>0.01</v>
       </c>
       <c r="I27" s="10">
-        <v>0.86</v>
+        <v>0.46</v>
       </c>
       <c r="J27" s="5">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D28">
         <v>2014</v>
@@ -7373,71 +7373,71 @@
         <v>41</v>
       </c>
       <c r="F28" s="10">
-        <v>0.49</v>
+        <v>1.35</v>
       </c>
       <c r="G28" s="9">
         <v>46295</v>
       </c>
       <c r="H28" s="10">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I28" s="10">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="J28" s="5">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29">
         <v>2014</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F29" s="10">
-        <v>0.9399999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="G29" s="9">
         <v>46295</v>
       </c>
       <c r="H29" s="10">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I29" s="10">
-        <v>0.76</v>
+        <v>0.17</v>
       </c>
       <c r="J29" s="5">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D30">
         <v>2014</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F30" s="10">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="G30" s="9">
         <v>46295</v>
@@ -7446,30 +7446,30 @@
         <v>0</v>
       </c>
       <c r="I30" s="10">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J30" s="5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D31">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E31" t="s">
         <v>41</v>
       </c>
       <c r="F31" s="10">
-        <v>1.12</v>
+        <v>0.28</v>
       </c>
       <c r="G31" s="9">
         <v>46295</v>
@@ -7478,21 +7478,21 @@
         <v>0</v>
       </c>
       <c r="I31" s="10">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="J31" s="5">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32">
         <v>2015</v>
@@ -7501,62 +7501,62 @@
         <v>41</v>
       </c>
       <c r="F32" s="10">
-        <v>2.4</v>
+        <v>1.23</v>
       </c>
       <c r="G32" s="9">
         <v>46295</v>
       </c>
       <c r="H32" s="10">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I32" s="10">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J32" s="5">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D33">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E33" t="s">
         <v>41</v>
       </c>
       <c r="F33" s="10">
-        <v>4.5</v>
+        <v>3.59</v>
       </c>
       <c r="G33" s="9">
         <v>46295</v>
       </c>
       <c r="H33" s="10">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I33" s="10">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J33" s="5">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D34">
         <v>2016</v>
@@ -7565,167 +7565,167 @@
         <v>41</v>
       </c>
       <c r="F34" s="10">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="G34" s="9">
         <v>46295</v>
       </c>
       <c r="H34" s="10">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I34" s="10">
-        <v>0.72</v>
+        <v>1.7</v>
       </c>
       <c r="J34" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D35">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F35" s="10">
-        <v>9.35</v>
+        <v>4.41</v>
       </c>
       <c r="G35" s="9">
         <v>46295</v>
       </c>
       <c r="H35" s="10">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I35" s="10">
-        <v>2.25</v>
+        <v>0.17</v>
       </c>
       <c r="J35" s="5">
-        <v>8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D36">
         <v>2017</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F36" s="10">
-        <v>4.94</v>
+        <v>10.11</v>
       </c>
       <c r="G36" s="9">
         <v>46295</v>
       </c>
       <c r="H36" s="10">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I36" s="10">
-        <v>1.41</v>
+        <v>0.91</v>
       </c>
       <c r="J36" s="5">
-        <v>3.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D37">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E37" t="s">
         <v>41</v>
       </c>
       <c r="F37" s="10">
-        <v>13.52</v>
+        <v>4.71</v>
       </c>
       <c r="G37" s="9">
         <v>46295</v>
       </c>
       <c r="H37" s="10">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I37" s="10">
-        <v>5</v>
+        <v>0.71</v>
       </c>
       <c r="J37" s="5">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D38">
         <v>2018</v>
       </c>
       <c r="E38" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F38" s="10">
-        <v>15.65</v>
+        <v>15.62</v>
       </c>
       <c r="G38" s="9">
         <v>46295</v>
       </c>
       <c r="H38" s="10">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I38" s="10">
-        <v>6.58</v>
+        <v>0.97</v>
       </c>
       <c r="J38" s="5">
-        <v>10.3</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D39">
         <v>2018</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F39" s="10">
-        <v>14.22</v>
+        <v>9.24</v>
       </c>
       <c r="G39" s="9">
         <v>46295</v>
@@ -7734,21 +7734,21 @@
         <v>0</v>
       </c>
       <c r="I39" s="10">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="J39" s="5">
-        <v>14.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B40" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D40">
         <v>2018</v>
@@ -7757,30 +7757,30 @@
         <v>41</v>
       </c>
       <c r="F40" s="10">
-        <v>13.64</v>
+        <v>16.16</v>
       </c>
       <c r="G40" s="9">
         <v>46295</v>
       </c>
       <c r="H40" s="10">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I40" s="10">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="J40" s="5">
-        <v>12.6</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D41">
         <v>2018</v>
@@ -7789,30 +7789,30 @@
         <v>41</v>
       </c>
       <c r="F41" s="10">
-        <v>11.63</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G41" s="9">
         <v>46295</v>
       </c>
       <c r="H41" s="10">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I41" s="10">
-        <v>2.98</v>
+        <v>0.36</v>
       </c>
       <c r="J41" s="5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D42">
         <v>2018</v>
@@ -7821,30 +7821,30 @@
         <v>41</v>
       </c>
       <c r="F42" s="10">
-        <v>9.41</v>
+        <v>14.19</v>
       </c>
       <c r="G42" s="9">
         <v>46295</v>
       </c>
       <c r="H42" s="10">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="I42" s="10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="J42" s="5">
-        <v>9.5</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D43">
         <v>2018</v>
@@ -7853,62 +7853,62 @@
         <v>41</v>
       </c>
       <c r="F43" s="10">
-        <v>23.71</v>
+        <v>13.66</v>
       </c>
       <c r="G43" s="9">
         <v>46295</v>
       </c>
       <c r="H43" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I43" s="10">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="J43" s="5">
-        <v>20.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D44">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E44" t="s">
         <v>41</v>
       </c>
       <c r="F44" s="10">
-        <v>16.14</v>
+        <v>23.62</v>
       </c>
       <c r="G44" s="9">
         <v>46295</v>
       </c>
       <c r="H44" s="10">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="I44" s="10">
-        <v>3.9</v>
+        <v>1.79</v>
       </c>
       <c r="J44" s="5">
-        <v>12.4</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D45">
         <v>2019</v>
@@ -7917,30 +7917,30 @@
         <v>41</v>
       </c>
       <c r="F45" s="10">
-        <v>19.25</v>
+        <v>15.13</v>
       </c>
       <c r="G45" s="9">
         <v>46295</v>
       </c>
       <c r="H45" s="10">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="I45" s="10">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="J45" s="5">
-        <v>19.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D46">
         <v>2019</v>
@@ -7949,30 +7949,30 @@
         <v>41</v>
       </c>
       <c r="F46" s="10">
-        <v>12.62</v>
+        <v>16.4</v>
       </c>
       <c r="G46" s="9">
         <v>46295</v>
       </c>
       <c r="H46" s="10">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I46" s="10">
-        <v>0.58</v>
+        <v>1.47</v>
       </c>
       <c r="J46" s="5">
-        <v>12.3</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D47">
         <v>2019</v>
@@ -7981,30 +7981,30 @@
         <v>41</v>
       </c>
       <c r="F47" s="10">
-        <v>23.3</v>
+        <v>15.09</v>
       </c>
       <c r="G47" s="9">
         <v>46295</v>
       </c>
       <c r="H47" s="10">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="I47" s="10">
-        <v>7.62</v>
+        <v>1.62</v>
       </c>
       <c r="J47" s="5">
-        <v>15.7</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B48" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D48">
         <v>2019</v>
@@ -8013,62 +8013,62 @@
         <v>41</v>
       </c>
       <c r="F48" s="10">
-        <v>20.5</v>
+        <v>16.17</v>
       </c>
       <c r="G48" s="9">
         <v>46295</v>
       </c>
       <c r="H48" s="10">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I48" s="10">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="J48" s="5">
-        <v>19.5</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D49">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E49" t="s">
         <v>41</v>
       </c>
       <c r="F49" s="10">
-        <v>20.12</v>
+        <v>14.11</v>
       </c>
       <c r="G49" s="9">
         <v>46295</v>
       </c>
       <c r="H49" s="10">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I49" s="10">
-        <v>3.17</v>
+        <v>0.39</v>
       </c>
       <c r="J49" s="5">
-        <v>17.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B50" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D50">
         <v>2020</v>
@@ -8077,30 +8077,30 @@
         <v>41</v>
       </c>
       <c r="F50" s="10">
-        <v>27.04</v>
+        <v>12.66</v>
       </c>
       <c r="G50" s="9">
         <v>46295</v>
       </c>
       <c r="H50" s="10">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="I50" s="10">
-        <v>3.22</v>
+        <v>0.14</v>
       </c>
       <c r="J50" s="5">
-        <v>23.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D51">
         <v>2020</v>
@@ -8109,126 +8109,126 @@
         <v>41</v>
       </c>
       <c r="F51" s="10">
-        <v>15.97</v>
+        <v>32.69</v>
       </c>
       <c r="G51" s="9">
         <v>46295</v>
       </c>
       <c r="H51" s="10">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I51" s="10">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="J51" s="5">
-        <v>15.8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="B52" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D52">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E52" t="s">
         <v>41</v>
       </c>
       <c r="F52" s="10">
-        <v>38.36</v>
+        <v>16.26</v>
       </c>
       <c r="G52" s="9">
         <v>46295</v>
       </c>
       <c r="H52" s="10">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I52" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J52" s="5">
-        <v>38.6</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B53" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D53">
         <v>2021</v>
       </c>
       <c r="E53" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F53" s="10">
-        <v>31.33</v>
+        <v>33.98</v>
       </c>
       <c r="G53" s="9">
         <v>46295</v>
       </c>
       <c r="H53" s="10">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="I53" s="10">
         <v>0</v>
       </c>
       <c r="J53" s="5">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B54" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D54">
         <v>2021</v>
       </c>
       <c r="E54" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F54" s="10">
-        <v>20.43</v>
+        <v>37.18</v>
       </c>
       <c r="G54" s="9">
         <v>46295</v>
       </c>
       <c r="H54" s="10">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I54" s="10">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="J54" s="5">
-        <v>20.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B55" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D55">
         <v>2021</v>
@@ -8237,30 +8237,30 @@
         <v>41</v>
       </c>
       <c r="F55" s="10">
-        <v>21.51</v>
+        <v>19.33</v>
       </c>
       <c r="G55" s="9">
         <v>46295</v>
       </c>
       <c r="H55" s="10">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I55" s="10">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="J55" s="5">
-        <v>21.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B56" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D56">
         <v>2021</v>
@@ -8269,126 +8269,126 @@
         <v>41</v>
       </c>
       <c r="F56" s="10">
-        <v>33.28</v>
+        <v>21.07</v>
       </c>
       <c r="G56" s="9">
         <v>46295</v>
       </c>
       <c r="H56" s="10">
-        <v>0.77</v>
+        <v>0.32</v>
       </c>
       <c r="I56" s="10">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="J56" s="5">
-        <v>29.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="B57" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D57">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E57" t="s">
         <v>41</v>
       </c>
       <c r="F57" s="10">
-        <v>22.34</v>
+        <v>47.8</v>
       </c>
       <c r="G57" s="9">
         <v>46295</v>
       </c>
       <c r="H57" s="10">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="I57" s="10">
-        <v>2.68</v>
+        <v>0.66</v>
       </c>
       <c r="J57" s="5">
-        <v>20.2</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D58">
         <v>2022</v>
       </c>
       <c r="E58" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F58" s="10">
-        <v>29.92</v>
+        <v>25.02</v>
       </c>
       <c r="G58" s="9">
         <v>46295</v>
       </c>
       <c r="H58" s="10">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="I58" s="10">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="J58" s="5">
-        <v>34.7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B59" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D59">
         <v>2022</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F59" s="10">
-        <v>23.5</v>
+        <v>30.58</v>
       </c>
       <c r="G59" s="9">
         <v>46295</v>
       </c>
       <c r="H59" s="10">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="I59" s="10">
-        <v>4.7</v>
+        <v>5.74</v>
       </c>
       <c r="J59" s="5">
-        <v>19.4</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B60" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D60">
         <v>2022</v>
@@ -8397,30 +8397,30 @@
         <v>41</v>
       </c>
       <c r="F60" s="10">
-        <v>20.47</v>
+        <v>30.88</v>
       </c>
       <c r="G60" s="9">
         <v>46295</v>
       </c>
       <c r="H60" s="10">
-        <v>0.64</v>
+        <v>1.35</v>
       </c>
       <c r="I60" s="10">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="J60" s="5">
-        <v>16.6</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B61" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D61">
         <v>2022</v>
@@ -8429,30 +8429,30 @@
         <v>41</v>
       </c>
       <c r="F61" s="10">
-        <v>24.1</v>
+        <v>17.2</v>
       </c>
       <c r="G61" s="9">
         <v>46295</v>
       </c>
       <c r="H61" s="10">
-        <v>0.92</v>
+        <v>0.39</v>
       </c>
       <c r="I61" s="10">
-        <v>1.55</v>
+        <v>0.18</v>
       </c>
       <c r="J61" s="5">
-        <v>23.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B62" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D62">
         <v>2022</v>
@@ -8461,190 +8461,190 @@
         <v>41</v>
       </c>
       <c r="F62" s="10">
-        <v>19.1</v>
+        <v>29.01</v>
       </c>
       <c r="G62" s="9">
         <v>46295</v>
       </c>
       <c r="H62" s="10">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="I62" s="10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="J62" s="5">
-        <v>19.8</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="B63" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D63">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="E63" t="s">
         <v>41</v>
       </c>
       <c r="F63" s="10">
-        <v>1.4</v>
+        <v>31.22</v>
       </c>
       <c r="G63" s="9">
         <v>46295</v>
       </c>
       <c r="H63" s="10">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="I63" s="10">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="J63" s="5">
-        <v>1.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B64" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D64">
         <v>2026</v>
       </c>
       <c r="E64" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F64" s="10">
-        <v>0.64</v>
+        <v>4.02</v>
       </c>
       <c r="G64" s="9">
         <v>46295</v>
       </c>
       <c r="H64" s="10">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="I64" s="10">
         <v>0</v>
       </c>
       <c r="J64" s="5">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B65" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D65">
         <v>2026</v>
       </c>
       <c r="E65" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F65" s="10">
-        <v>0.03</v>
+        <v>3.36</v>
       </c>
       <c r="G65" s="9">
         <v>46295</v>
       </c>
       <c r="H65" s="10">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="I65" s="10">
         <v>0</v>
       </c>
       <c r="J65" s="5">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B66" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D66">
         <v>2026</v>
       </c>
       <c r="E66" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F66" s="10">
-        <v>17.52</v>
+        <v>2.64</v>
       </c>
       <c r="G66" s="9">
         <v>46295</v>
       </c>
       <c r="H66" s="10">
-        <v>1.32</v>
+        <v>0.26</v>
       </c>
       <c r="I66" s="10">
         <v>0</v>
       </c>
       <c r="J66" s="5">
-        <v>21.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B67" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D67">
         <v>2026</v>
       </c>
       <c r="E67" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F67" s="10">
-        <v>-0.09</v>
+        <v>18.57</v>
       </c>
       <c r="G67" s="9">
         <v>46295</v>
       </c>
       <c r="H67" s="10">
-        <v>0.22</v>
+        <v>8.1</v>
       </c>
       <c r="I67" s="10">
         <v>0</v>
       </c>
       <c r="J67" s="5">
-        <v>0.1</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B68" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D68">
         <v>2026</v>
@@ -8653,71 +8653,71 @@
         <v>41</v>
       </c>
       <c r="F68" s="10">
-        <v>0.34</v>
+        <v>2.76</v>
       </c>
       <c r="G68" s="9">
         <v>46295</v>
       </c>
       <c r="H68" s="10">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="I68" s="10">
         <v>0</v>
       </c>
       <c r="J68" s="5">
-        <v>0.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>45</v>
+        <v>328</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>329</v>
       </c>
       <c r="C69" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D69">
-        <v>2009</v>
+        <v>2026</v>
       </c>
       <c r="E69" t="s">
         <v>41</v>
       </c>
       <c r="F69" s="10">
-        <v>0.04</v>
+        <v>4.11</v>
       </c>
       <c r="G69" s="9">
         <v>46295</v>
       </c>
       <c r="H69" s="10">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="I69" s="10">
         <v>0</v>
       </c>
       <c r="J69" s="5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D70">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E70" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F70" s="10">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="G70" s="9">
         <v>46295</v>
@@ -8726,7 +8726,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="10">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="J70" s="5">
         <v>0.1</v>
@@ -8734,22 +8734,22 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C71" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D71">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E71" t="s">
         <v>41</v>
       </c>
       <c r="F71" s="10">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G71" s="9">
         <v>46295</v>
@@ -8766,13 +8766,13 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C72" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D72">
         <v>2012</v>
@@ -8781,7 +8781,7 @@
         <v>41</v>
       </c>
       <c r="F72" s="10">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="G72" s="9">
         <v>46295</v>
@@ -8790,21 +8790,21 @@
         <v>0</v>
       </c>
       <c r="I72" s="10">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J72" s="5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D73">
         <v>2013</v>
@@ -8813,7 +8813,7 @@
         <v>41</v>
       </c>
       <c r="F73" s="10">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="G73" s="9">
         <v>46295</v>
@@ -8822,10 +8822,10 @@
         <v>0</v>
       </c>
       <c r="I73" s="10">
-        <v>0.17</v>
+        <v>0.74</v>
       </c>
       <c r="J73" s="5">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -8836,7 +8836,7 @@
         <v>102</v>
       </c>
       <c r="C74" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D74">
         <v>2014</v>
@@ -8845,7 +8845,7 @@
         <v>41</v>
       </c>
       <c r="F74" s="10">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="G74" s="9">
         <v>46295</v>
@@ -8854,10 +8854,10 @@
         <v>0</v>
       </c>
       <c r="I74" s="10">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="J74" s="5">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -8868,7 +8868,7 @@
         <v>106</v>
       </c>
       <c r="C75" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D75">
         <v>2014</v>
@@ -8877,7 +8877,7 @@
         <v>41</v>
       </c>
       <c r="F75" s="10">
-        <v>0.37</v>
+        <v>1.15</v>
       </c>
       <c r="G75" s="9">
         <v>46295</v>
@@ -8886,10 +8886,10 @@
         <v>0</v>
       </c>
       <c r="I75" s="10">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="J75" s="5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -8900,16 +8900,16 @@
         <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D76">
         <v>2014</v>
       </c>
       <c r="E76" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F76" s="10">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
       <c r="G76" s="9">
         <v>46295</v>
@@ -8918,10 +8918,10 @@
         <v>0</v>
       </c>
       <c r="I76" s="10">
-        <v>0.6899999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="J76" s="5">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -8932,7 +8932,7 @@
         <v>136</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D77">
         <v>2015</v>
@@ -8941,19 +8941,19 @@
         <v>41</v>
       </c>
       <c r="F77" s="10">
-        <v>3.07</v>
+        <v>2.72</v>
       </c>
       <c r="G77" s="9">
         <v>46295</v>
       </c>
       <c r="H77" s="10">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I77" s="10">
-        <v>0.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J77" s="5">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -8964,7 +8964,7 @@
         <v>126</v>
       </c>
       <c r="C78" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D78">
         <v>2015</v>
@@ -8973,7 +8973,7 @@
         <v>41</v>
       </c>
       <c r="F78" s="10">
-        <v>2.85</v>
+        <v>3.36</v>
       </c>
       <c r="G78" s="9">
         <v>46295</v>
@@ -8982,10 +8982,10 @@
         <v>0</v>
       </c>
       <c r="I78" s="10">
-        <v>0.07000000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J78" s="5">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -8996,7 +8996,7 @@
         <v>122</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D79">
         <v>2015</v>
@@ -9005,19 +9005,19 @@
         <v>41</v>
       </c>
       <c r="F79" s="10">
-        <v>0.61</v>
+        <v>1.76</v>
       </c>
       <c r="G79" s="9">
         <v>46295</v>
       </c>
       <c r="H79" s="10">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I79" s="10">
-        <v>0.28</v>
+        <v>0.86</v>
       </c>
       <c r="J79" s="5">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -9028,28 +9028,28 @@
         <v>163</v>
       </c>
       <c r="C80" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D80">
         <v>2016</v>
       </c>
       <c r="E80" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F80" s="10">
-        <v>4.72</v>
+        <v>3.83</v>
       </c>
       <c r="G80" s="9">
         <v>46295</v>
       </c>
       <c r="H80" s="10">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I80" s="10">
-        <v>0.18</v>
+        <v>1.4</v>
       </c>
       <c r="J80" s="5">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -9060,7 +9060,7 @@
         <v>151</v>
       </c>
       <c r="C81" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D81">
         <v>2016</v>
@@ -9069,19 +9069,19 @@
         <v>41</v>
       </c>
       <c r="F81" s="10">
-        <v>7.4</v>
+        <v>4.65</v>
       </c>
       <c r="G81" s="9">
         <v>46295</v>
       </c>
       <c r="H81" s="10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I81" s="10">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="J81" s="5">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -9092,7 +9092,7 @@
         <v>155</v>
       </c>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D82">
         <v>2016</v>
@@ -9101,19 +9101,19 @@
         <v>41</v>
       </c>
       <c r="F82" s="10">
-        <v>5.81</v>
+        <v>2.3</v>
       </c>
       <c r="G82" s="9">
         <v>46295</v>
       </c>
       <c r="H82" s="10">
+        <v>0</v>
+      </c>
+      <c r="I82" s="10">
         <v>0.06</v>
       </c>
-      <c r="I82" s="10">
-        <v>0</v>
-      </c>
       <c r="J82" s="5">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -9124,16 +9124,16 @@
         <v>147</v>
       </c>
       <c r="C83" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D83">
         <v>2016</v>
       </c>
       <c r="E83" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F83" s="10">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="G83" s="9">
         <v>46295</v>
@@ -9142,10 +9142,10 @@
         <v>0</v>
       </c>
       <c r="I83" s="10">
-        <v>0.7</v>
+        <v>0.03</v>
       </c>
       <c r="J83" s="5">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -9156,7 +9156,7 @@
         <v>165</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D84">
         <v>2016</v>
@@ -9165,7 +9165,7 @@
         <v>41</v>
       </c>
       <c r="F84" s="10">
-        <v>5.1</v>
+        <v>6.3</v>
       </c>
       <c r="G84" s="9">
         <v>46295</v>
@@ -9174,10 +9174,10 @@
         <v>0</v>
       </c>
       <c r="I84" s="10">
-        <v>0.12</v>
+        <v>1.54</v>
       </c>
       <c r="J84" s="5">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -9188,7 +9188,7 @@
         <v>183</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D85">
         <v>2017</v>
@@ -9197,7 +9197,7 @@
         <v>41</v>
       </c>
       <c r="F85" s="10">
-        <v>5.56</v>
+        <v>7.1</v>
       </c>
       <c r="G85" s="9">
         <v>46295</v>
@@ -9206,10 +9206,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="10">
-        <v>0.64</v>
+        <v>1.53</v>
       </c>
       <c r="J85" s="5">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -9220,7 +9220,7 @@
         <v>177</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D86">
         <v>2017</v>
@@ -9229,7 +9229,7 @@
         <v>41</v>
       </c>
       <c r="F86" s="10">
-        <v>9.32</v>
+        <v>4.14</v>
       </c>
       <c r="G86" s="9">
         <v>46295</v>
@@ -9238,10 +9238,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I86" s="10">
-        <v>1.45</v>
+        <v>0.03</v>
       </c>
       <c r="J86" s="5">
-        <v>8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -9252,7 +9252,7 @@
         <v>185</v>
       </c>
       <c r="C87" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D87">
         <v>2017</v>
@@ -9261,7 +9261,7 @@
         <v>41</v>
       </c>
       <c r="F87" s="10">
-        <v>8.99</v>
+        <v>7.55</v>
       </c>
       <c r="G87" s="9">
         <v>46295</v>
@@ -9270,10 +9270,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="10">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="J87" s="5">
-        <v>9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -9284,28 +9284,28 @@
         <v>173</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D88">
         <v>2017</v>
       </c>
       <c r="E88" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F88" s="10">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="G88" s="9">
         <v>46295</v>
       </c>
       <c r="H88" s="10">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I88" s="10">
-        <v>0.11</v>
+        <v>1.24</v>
       </c>
       <c r="J88" s="5">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -9316,7 +9316,7 @@
         <v>199</v>
       </c>
       <c r="C89" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D89">
         <v>2018</v>
@@ -9325,19 +9325,19 @@
         <v>41</v>
       </c>
       <c r="F89" s="10">
-        <v>6.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G89" s="9">
         <v>46295</v>
       </c>
       <c r="H89" s="10">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I89" s="10">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="J89" s="5">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -9348,7 +9348,7 @@
         <v>195</v>
       </c>
       <c r="C90" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D90">
         <v>2018</v>
@@ -9357,7 +9357,7 @@
         <v>41</v>
       </c>
       <c r="F90" s="10">
-        <v>17.43</v>
+        <v>8.76</v>
       </c>
       <c r="G90" s="9">
         <v>46295</v>
@@ -9366,10 +9366,10 @@
         <v>0</v>
       </c>
       <c r="I90" s="10">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="J90" s="5">
-        <v>14.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -9380,7 +9380,7 @@
         <v>231</v>
       </c>
       <c r="C91" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D91">
         <v>2019</v>
@@ -9389,19 +9389,19 @@
         <v>41</v>
       </c>
       <c r="F91" s="10">
-        <v>14.26</v>
+        <v>12.19</v>
       </c>
       <c r="G91" s="9">
         <v>46295</v>
       </c>
       <c r="H91" s="10">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="I91" s="10">
-        <v>2.42</v>
+        <v>1.72</v>
       </c>
       <c r="J91" s="5">
-        <v>12</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -9412,7 +9412,7 @@
         <v>221</v>
       </c>
       <c r="C92" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D92">
         <v>2019</v>
@@ -9421,19 +9421,19 @@
         <v>41</v>
       </c>
       <c r="F92" s="10">
-        <v>7.96</v>
+        <v>13.13</v>
       </c>
       <c r="G92" s="9">
         <v>46295</v>
       </c>
       <c r="H92" s="10">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="I92" s="10">
-        <v>0.14</v>
+        <v>3.26</v>
       </c>
       <c r="J92" s="5">
-        <v>8</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -9444,7 +9444,7 @@
         <v>229</v>
       </c>
       <c r="C93" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D93">
         <v>2019</v>
@@ -9453,19 +9453,19 @@
         <v>41</v>
       </c>
       <c r="F93" s="10">
-        <v>16.42</v>
+        <v>18.45</v>
       </c>
       <c r="G93" s="9">
         <v>46295</v>
       </c>
       <c r="H93" s="10">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="I93" s="10">
-        <v>1.06</v>
+        <v>2.47</v>
       </c>
       <c r="J93" s="5">
-        <v>15.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -9476,7 +9476,7 @@
         <v>233</v>
       </c>
       <c r="C94" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D94">
         <v>2019</v>
@@ -9485,19 +9485,19 @@
         <v>41</v>
       </c>
       <c r="F94" s="10">
-        <v>15.54</v>
+        <v>17.56</v>
       </c>
       <c r="G94" s="9">
         <v>46295</v>
       </c>
       <c r="H94" s="10">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="I94" s="10">
-        <v>2.85</v>
+        <v>0.98</v>
       </c>
       <c r="J94" s="5">
-        <v>12.8</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -9508,7 +9508,7 @@
         <v>249</v>
       </c>
       <c r="C95" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D95">
         <v>2020</v>
@@ -9517,19 +9517,19 @@
         <v>41</v>
       </c>
       <c r="F95" s="10">
-        <v>20.58</v>
+        <v>15.57</v>
       </c>
       <c r="G95" s="9">
         <v>46295</v>
       </c>
       <c r="H95" s="10">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="I95" s="10">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="J95" s="5">
-        <v>18.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D96">
         <v>2020</v>
@@ -9549,19 +9549,19 @@
         <v>41</v>
       </c>
       <c r="F96" s="10">
-        <v>8.640000000000001</v>
+        <v>14.76</v>
       </c>
       <c r="G96" s="9">
         <v>46295</v>
       </c>
       <c r="H96" s="10">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I96" s="10">
         <v>0</v>
       </c>
       <c r="J96" s="5">
-        <v>8.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -9572,7 +9572,7 @@
         <v>261</v>
       </c>
       <c r="C97" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D97">
         <v>2020</v>
@@ -9581,19 +9581,19 @@
         <v>41</v>
       </c>
       <c r="F97" s="10">
-        <v>21.01</v>
+        <v>24.78</v>
       </c>
       <c r="G97" s="9">
         <v>46295</v>
       </c>
       <c r="H97" s="10">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I97" s="10">
-        <v>3.04</v>
+        <v>4.54</v>
       </c>
       <c r="J97" s="5">
-        <v>18.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -9604,7 +9604,7 @@
         <v>255</v>
       </c>
       <c r="C98" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D98">
         <v>2020</v>
@@ -9613,19 +9613,19 @@
         <v>41</v>
       </c>
       <c r="F98" s="10">
-        <v>17.64</v>
+        <v>15.12</v>
       </c>
       <c r="G98" s="9">
         <v>46295</v>
       </c>
       <c r="H98" s="10">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="I98" s="10">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="J98" s="5">
-        <v>14.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -9636,28 +9636,28 @@
         <v>263</v>
       </c>
       <c r="C99" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D99">
         <v>2021</v>
       </c>
       <c r="E99" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F99" s="10">
-        <v>18.31</v>
+        <v>19.99</v>
       </c>
       <c r="G99" s="9">
         <v>46295</v>
       </c>
       <c r="H99" s="10">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="I99" s="10">
-        <v>2.82</v>
+        <v>0.36</v>
       </c>
       <c r="J99" s="5">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -9668,7 +9668,7 @@
         <v>267</v>
       </c>
       <c r="C100" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D100">
         <v>2021</v>
@@ -9677,19 +9677,19 @@
         <v>41</v>
       </c>
       <c r="F100" s="10">
-        <v>28.38</v>
+        <v>23.02</v>
       </c>
       <c r="G100" s="9">
         <v>46295</v>
       </c>
       <c r="H100" s="10">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="I100" s="10">
-        <v>1.06</v>
+        <v>7.23</v>
       </c>
       <c r="J100" s="5">
-        <v>27.5</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -9700,7 +9700,7 @@
         <v>283</v>
       </c>
       <c r="C101" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D101">
         <v>2021</v>
@@ -9709,19 +9709,19 @@
         <v>41</v>
       </c>
       <c r="F101" s="10">
-        <v>17.6</v>
+        <v>21.85</v>
       </c>
       <c r="G101" s="9">
         <v>46295</v>
       </c>
       <c r="H101" s="10">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I101" s="10">
-        <v>0.6899999999999999</v>
+        <v>2.58</v>
       </c>
       <c r="J101" s="5">
-        <v>16.9</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -9732,7 +9732,7 @@
         <v>323</v>
       </c>
       <c r="C102" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D102">
         <v>2026</v>
@@ -9741,19 +9741,19 @@
         <v>41</v>
       </c>
       <c r="F102" s="10">
-        <v>0.89</v>
+        <v>4.04</v>
       </c>
       <c r="G102" s="9">
         <v>46295</v>
       </c>
       <c r="H102" s="10">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I102" s="10">
         <v>0</v>
       </c>
       <c r="J102" s="5">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -9764,28 +9764,28 @@
         <v>337</v>
       </c>
       <c r="C103" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D103">
         <v>2026</v>
       </c>
       <c r="E103" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F103" s="10">
-        <v>0.43</v>
+        <v>3.44</v>
       </c>
       <c r="G103" s="9">
         <v>46295</v>
       </c>
       <c r="H103" s="10">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I103" s="10">
         <v>0</v>
       </c>
       <c r="J103" s="5">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -9796,7 +9796,7 @@
         <v>331</v>
       </c>
       <c r="C104" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D104">
         <v>2026</v>
@@ -9805,19 +9805,19 @@
         <v>41</v>
       </c>
       <c r="F104" s="10">
-        <v>1.28</v>
+        <v>3.85</v>
       </c>
       <c r="G104" s="9">
         <v>46295</v>
       </c>
       <c r="H104" s="10">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="I104" s="10">
         <v>0</v>
       </c>
       <c r="J104" s="5">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -9837,7 +9837,7 @@
         <v>41</v>
       </c>
       <c r="F105" s="10">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G105" s="9">
         <v>46356</v>
@@ -9846,7 +9846,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J105" s="5">
         <v>0</v>
@@ -9866,10 +9866,10 @@
         <v>2016</v>
       </c>
       <c r="E106" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F106" s="10">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="G106" s="9">
         <v>46356</v>
@@ -9878,10 +9878,10 @@
         <v>0.02</v>
       </c>
       <c r="I106" s="10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -9898,10 +9898,10 @@
         <v>2017</v>
       </c>
       <c r="E107" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F107" s="10">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="G107" s="9">
         <v>46356</v>
@@ -9913,7 +9913,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -9930,10 +9930,10 @@
         <v>2018</v>
       </c>
       <c r="E108" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F108" s="10">
-        <v>1.15</v>
+        <v>2.22</v>
       </c>
       <c r="G108" s="9">
         <v>46356</v>
@@ -9942,10 +9942,10 @@
         <v>0</v>
       </c>
       <c r="I108" s="10">
-        <v>0.01</v>
+        <v>0.18</v>
       </c>
       <c r="J108" s="5">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -9965,7 +9965,7 @@
         <v>41</v>
       </c>
       <c r="F109" s="10">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="G109" s="9">
         <v>46356</v>
@@ -9974,10 +9974,10 @@
         <v>0</v>
       </c>
       <c r="I109" s="10">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
       <c r="J109" s="5">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -9994,22 +9994,22 @@
         <v>2021</v>
       </c>
       <c r="E110" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F110" s="10">
-        <v>7.19</v>
+        <v>7.38</v>
       </c>
       <c r="G110" s="9">
         <v>46356</v>
       </c>
       <c r="H110" s="10">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I110" s="10">
-        <v>0.08</v>
+        <v>0.77</v>
       </c>
       <c r="J110" s="5">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -10026,10 +10026,10 @@
         <v>2021</v>
       </c>
       <c r="E111" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F111" s="10">
-        <v>7.77</v>
+        <v>5.79</v>
       </c>
       <c r="G111" s="9">
         <v>46356</v>
@@ -10038,10 +10038,10 @@
         <v>0</v>
       </c>
       <c r="I111" s="10">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="J111" s="5">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -10058,22 +10058,22 @@
         <v>2022</v>
       </c>
       <c r="E112" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F112" s="10">
-        <v>12.37</v>
+        <v>14.6</v>
       </c>
       <c r="G112" s="9">
         <v>46356</v>
       </c>
       <c r="H112" s="10">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I112" s="10">
-        <v>0.93</v>
+        <v>0.33</v>
       </c>
       <c r="J112" s="5">
-        <v>13.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -10093,7 +10093,7 @@
         <v>41</v>
       </c>
       <c r="F113" s="10">
-        <v>-0.37</v>
+        <v>3.05</v>
       </c>
       <c r="G113" s="9">
         <v>46356</v>
@@ -10105,7 +10105,7 @@
         <v>0.12</v>
       </c>
       <c r="J113" s="5">
-        <v>-0.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -10125,33 +10125,33 @@
         <v>41</v>
       </c>
       <c r="F114" s="10">
-        <v>-0.32</v>
+        <v>3.69</v>
       </c>
       <c r="G114" s="9">
         <v>46356</v>
       </c>
       <c r="H114" s="10">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="I114" s="10">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="J114" s="5">
-        <v>-0.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B115" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C115" t="s">
         <v>40</v>
       </c>
       <c r="D115">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E115" t="s">
         <v>41</v>
@@ -10174,22 +10174,22 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B116" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C116" t="s">
         <v>40</v>
       </c>
       <c r="D116">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="E116" t="s">
         <v>41</v>
       </c>
       <c r="F116" s="10">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="G116" s="9">
         <v>46203</v>
@@ -10198,18 +10198,18 @@
         <v>0</v>
       </c>
       <c r="I116" s="10">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J116" s="5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>47</v>
+      </c>
+      <c r="B117" t="s">
         <v>48</v>
-      </c>
-      <c r="B117" t="s">
-        <v>49</v>
       </c>
       <c r="C117" t="s">
         <v>40</v>
@@ -10221,7 +10221,7 @@
         <v>41</v>
       </c>
       <c r="F117" s="10">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G117" s="9">
         <v>46203</v>
@@ -10230,18 +10230,18 @@
         <v>0</v>
       </c>
       <c r="I117" s="10">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J117" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C118" t="s">
         <v>40</v>
@@ -10253,7 +10253,7 @@
         <v>41</v>
       </c>
       <c r="F118" s="10">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
       <c r="G118" s="9">
         <v>46203</v>
@@ -10262,18 +10262,18 @@
         <v>0</v>
       </c>
       <c r="I118" s="10">
+        <v>0.14</v>
+      </c>
+      <c r="J118" s="5">
         <v>0.2</v>
-      </c>
-      <c r="J118" s="5">
-        <v>0.7</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B119" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C119" t="s">
         <v>40</v>
@@ -10285,7 +10285,7 @@
         <v>41</v>
       </c>
       <c r="F119" s="10">
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="G119" s="9">
         <v>46203</v>
@@ -10294,18 +10294,18 @@
         <v>0</v>
       </c>
       <c r="I119" s="10">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J119" s="5">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B120" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C120" t="s">
         <v>40</v>
@@ -10317,7 +10317,7 @@
         <v>41</v>
       </c>
       <c r="F120" s="10">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="G120" s="9">
         <v>46203</v>
@@ -10326,18 +10326,18 @@
         <v>0</v>
       </c>
       <c r="I120" s="10">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J120" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B121" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C121" t="s">
         <v>40</v>
@@ -10349,7 +10349,7 @@
         <v>41</v>
       </c>
       <c r="F121" s="10">
-        <v>4.43</v>
+        <v>1.01</v>
       </c>
       <c r="G121" s="9">
         <v>46203</v>
@@ -10358,18 +10358,18 @@
         <v>0</v>
       </c>
       <c r="I121" s="10">
-        <v>4.02</v>
+        <v>0.12</v>
       </c>
       <c r="J121" s="5">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B122" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C122" t="s">
         <v>40</v>
@@ -10381,7 +10381,7 @@
         <v>41</v>
       </c>
       <c r="F122" s="10">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="G122" s="9">
         <v>46203</v>
@@ -10390,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="10">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="J122" s="5">
         <v>0.1</v>
@@ -10398,10 +10398,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B123" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C123" t="s">
         <v>40</v>
@@ -10413,7 +10413,7 @@
         <v>41</v>
       </c>
       <c r="F123" s="10">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="G123" s="9">
         <v>46203</v>
@@ -10422,18 +10422,18 @@
         <v>0</v>
       </c>
       <c r="I123" s="10">
-        <v>1.41</v>
+        <v>0.02</v>
       </c>
       <c r="J123" s="5">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C124" t="s">
         <v>40</v>
@@ -10445,7 +10445,7 @@
         <v>41</v>
       </c>
       <c r="F124" s="10">
-        <v>0.93</v>
+        <v>3.41</v>
       </c>
       <c r="G124" s="9">
         <v>46203</v>
@@ -10454,18 +10454,18 @@
         <v>0</v>
       </c>
       <c r="I124" s="10">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="J124" s="5">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B125" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C125" t="s">
         <v>40</v>
@@ -10477,7 +10477,7 @@
         <v>41</v>
       </c>
       <c r="F125" s="10">
-        <v>2.09</v>
+        <v>2.78</v>
       </c>
       <c r="G125" s="9">
         <v>46203</v>
@@ -10486,18 +10486,18 @@
         <v>0</v>
       </c>
       <c r="I125" s="10">
-        <v>0.6899999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="J125" s="5">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B126" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C126" t="s">
         <v>40</v>
@@ -10509,7 +10509,7 @@
         <v>41</v>
       </c>
       <c r="F126" s="10">
-        <v>5.57</v>
+        <v>3.58</v>
       </c>
       <c r="G126" s="9">
         <v>46203</v>
@@ -10518,10 +10518,10 @@
         <v>0</v>
       </c>
       <c r="I126" s="10">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="J126" s="5">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -10541,7 +10541,7 @@
         <v>41</v>
       </c>
       <c r="F127" s="10">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="G127" s="9">
         <v>46203</v>
@@ -10550,10 +10550,10 @@
         <v>0</v>
       </c>
       <c r="I127" s="10">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="J127" s="5">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -10573,7 +10573,7 @@
         <v>41</v>
       </c>
       <c r="F128" s="10">
-        <v>3.85</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G128" s="9">
         <v>46203</v>
@@ -10582,10 +10582,10 @@
         <v>0</v>
       </c>
       <c r="I128" s="10">
-        <v>0.15</v>
+        <v>2.04</v>
       </c>
       <c r="J128" s="5">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -10605,7 +10605,7 @@
         <v>41</v>
       </c>
       <c r="F129" s="10">
-        <v>4.86</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G129" s="9">
         <v>46203</v>
@@ -10614,10 +10614,10 @@
         <v>0</v>
       </c>
       <c r="I129" s="10">
-        <v>1.24</v>
+        <v>0.47</v>
       </c>
       <c r="J129" s="5">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -10637,7 +10637,7 @@
         <v>41</v>
       </c>
       <c r="F130" s="10">
-        <v>3.72</v>
+        <v>4.29</v>
       </c>
       <c r="G130" s="9">
         <v>46203</v>
@@ -10646,10 +10646,10 @@
         <v>0</v>
       </c>
       <c r="I130" s="10">
-        <v>0.48</v>
+        <v>0.87</v>
       </c>
       <c r="J130" s="5">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -10669,7 +10669,7 @@
         <v>41</v>
       </c>
       <c r="F131" s="10">
-        <v>8.84</v>
+        <v>6.53</v>
       </c>
       <c r="G131" s="9">
         <v>46203</v>
@@ -10678,10 +10678,10 @@
         <v>0</v>
       </c>
       <c r="I131" s="10">
-        <v>3.44</v>
+        <v>1.71</v>
       </c>
       <c r="J131" s="5">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -10701,7 +10701,7 @@
         <v>41</v>
       </c>
       <c r="F132" s="10">
-        <v>8.390000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G132" s="9">
         <v>46203</v>
@@ -10710,10 +10710,10 @@
         <v>0</v>
       </c>
       <c r="I132" s="10">
-        <v>0.68</v>
+        <v>2.83</v>
       </c>
       <c r="J132" s="5">
-        <v>7.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -10733,19 +10733,19 @@
         <v>41</v>
       </c>
       <c r="F133" s="10">
-        <v>8.369999999999999</v>
+        <v>11.89</v>
       </c>
       <c r="G133" s="9">
         <v>46203</v>
       </c>
       <c r="H133" s="10">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I133" s="10">
-        <v>1.66</v>
+        <v>3.74</v>
       </c>
       <c r="J133" s="5">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -10765,19 +10765,19 @@
         <v>41</v>
       </c>
       <c r="F134" s="10">
-        <v>10.47</v>
+        <v>11.01</v>
       </c>
       <c r="G134" s="9">
         <v>46203</v>
       </c>
       <c r="H134" s="10">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I134" s="10">
-        <v>1.07</v>
+        <v>2.35</v>
       </c>
       <c r="J134" s="5">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -10797,7 +10797,7 @@
         <v>41</v>
       </c>
       <c r="F135" s="10">
-        <v>10.26</v>
+        <v>14.36</v>
       </c>
       <c r="G135" s="9">
         <v>46203</v>
@@ -10806,10 +10806,10 @@
         <v>0</v>
       </c>
       <c r="I135" s="10">
-        <v>2.84</v>
+        <v>13.44</v>
       </c>
       <c r="J135" s="5">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -10829,19 +10829,19 @@
         <v>41</v>
       </c>
       <c r="F136" s="10">
-        <v>7.58</v>
+        <v>8.5</v>
       </c>
       <c r="G136" s="9">
         <v>46203</v>
       </c>
       <c r="H136" s="10">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I136" s="10">
-        <v>0.92</v>
+        <v>1.94</v>
       </c>
       <c r="J136" s="5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -10861,19 +10861,19 @@
         <v>41</v>
       </c>
       <c r="F137" s="10">
-        <v>5.15</v>
+        <v>6.17</v>
       </c>
       <c r="G137" s="9">
         <v>46203</v>
       </c>
       <c r="H137" s="10">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I137" s="10">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="J137" s="5">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -10893,7 +10893,7 @@
         <v>41</v>
       </c>
       <c r="F138" s="10">
-        <v>17.28</v>
+        <v>13.51</v>
       </c>
       <c r="G138" s="9">
         <v>46203</v>
@@ -10902,10 +10902,10 @@
         <v>0</v>
       </c>
       <c r="I138" s="10">
-        <v>2.49</v>
+        <v>1.08</v>
       </c>
       <c r="J138" s="5">
-        <v>14.8</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -10925,19 +10925,19 @@
         <v>41</v>
       </c>
       <c r="F139" s="10">
-        <v>8.18</v>
+        <v>11.52</v>
       </c>
       <c r="G139" s="9">
         <v>46203</v>
       </c>
       <c r="H139" s="10">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I139" s="10">
-        <v>1.73</v>
+        <v>4.1</v>
       </c>
       <c r="J139" s="5">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -10957,7 +10957,7 @@
         <v>41</v>
       </c>
       <c r="F140" s="10">
-        <v>22.39</v>
+        <v>19.52</v>
       </c>
       <c r="G140" s="9">
         <v>46203</v>
@@ -10966,10 +10966,10 @@
         <v>0</v>
       </c>
       <c r="I140" s="10">
-        <v>14.02</v>
+        <v>2.58</v>
       </c>
       <c r="J140" s="5">
-        <v>8.4</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -10989,19 +10989,19 @@
         <v>41</v>
       </c>
       <c r="F141" s="10">
-        <v>16.6</v>
+        <v>16.16</v>
       </c>
       <c r="G141" s="9">
         <v>46203</v>
       </c>
       <c r="H141" s="10">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I141" s="10">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="J141" s="5">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -11021,19 +11021,19 @@
         <v>41</v>
       </c>
       <c r="F142" s="10">
-        <v>5.78</v>
+        <v>13.09</v>
       </c>
       <c r="G142" s="9">
         <v>46203</v>
       </c>
       <c r="H142" s="10">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I142" s="10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J142" s="5">
-        <v>5.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -11053,19 +11053,19 @@
         <v>41</v>
       </c>
       <c r="F143" s="10">
-        <v>12.78</v>
+        <v>17.15</v>
       </c>
       <c r="G143" s="9">
         <v>46203</v>
       </c>
       <c r="H143" s="10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I143" s="10">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="J143" s="5">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -11085,7 +11085,7 @@
         <v>41</v>
       </c>
       <c r="F144" s="10">
-        <v>40.64</v>
+        <v>28.04</v>
       </c>
       <c r="G144" s="9">
         <v>46203</v>
@@ -11094,10 +11094,10 @@
         <v>0</v>
       </c>
       <c r="I144" s="10">
-        <v>24.95</v>
+        <v>11.68</v>
       </c>
       <c r="J144" s="5">
-        <v>15.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -11117,19 +11117,19 @@
         <v>41</v>
       </c>
       <c r="F145" s="10">
-        <v>13.5</v>
+        <v>9.19</v>
       </c>
       <c r="G145" s="9">
         <v>46203</v>
       </c>
       <c r="H145" s="10">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="I145" s="10">
-        <v>0.78</v>
+        <v>1.12</v>
       </c>
       <c r="J145" s="5">
-        <v>12.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -11149,19 +11149,19 @@
         <v>41</v>
       </c>
       <c r="F146" s="10">
-        <v>17.14</v>
+        <v>29.99</v>
       </c>
       <c r="G146" s="9">
         <v>46203</v>
       </c>
       <c r="H146" s="10">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I146" s="10">
-        <v>3.08</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="J146" s="5">
-        <v>15.4</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -11181,19 +11181,19 @@
         <v>41</v>
       </c>
       <c r="F147" s="10">
-        <v>16.29</v>
+        <v>20.03</v>
       </c>
       <c r="G147" s="9">
         <v>46203</v>
       </c>
       <c r="H147" s="10">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="I147" s="10">
-        <v>1.5</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="J147" s="5">
-        <v>15.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -11213,7 +11213,7 @@
         <v>41</v>
       </c>
       <c r="F148" s="10">
-        <v>43.38</v>
+        <v>37.02</v>
       </c>
       <c r="G148" s="9">
         <v>46203</v>
@@ -11222,10 +11222,10 @@
         <v>0</v>
       </c>
       <c r="I148" s="10">
-        <v>5.61</v>
+        <v>3.27</v>
       </c>
       <c r="J148" s="5">
-        <v>37.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -11245,19 +11245,19 @@
         <v>41</v>
       </c>
       <c r="F149" s="10">
-        <v>24.87</v>
+        <v>16.44</v>
       </c>
       <c r="G149" s="9">
         <v>46203</v>
       </c>
       <c r="H149" s="10">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="I149" s="10">
-        <v>2.34</v>
+        <v>0.63</v>
       </c>
       <c r="J149" s="5">
-        <v>23.2</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -11277,19 +11277,19 @@
         <v>41</v>
       </c>
       <c r="F150" s="10">
-        <v>42.27</v>
+        <v>15.69</v>
       </c>
       <c r="G150" s="9">
         <v>46203</v>
       </c>
       <c r="H150" s="10">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="I150" s="10">
-        <v>37.08</v>
+        <v>0.13</v>
       </c>
       <c r="J150" s="5">
-        <v>5.6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -11309,19 +11309,19 @@
         <v>41</v>
       </c>
       <c r="F151" s="10">
-        <v>21.96</v>
+        <v>39.08</v>
       </c>
       <c r="G151" s="9">
         <v>46203</v>
       </c>
       <c r="H151" s="10">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I151" s="10">
-        <v>5.5</v>
+        <v>7.89</v>
       </c>
       <c r="J151" s="5">
-        <v>16.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -11341,19 +11341,19 @@
         <v>41</v>
       </c>
       <c r="F152" s="10">
-        <v>13.07</v>
+        <v>18.1</v>
       </c>
       <c r="G152" s="9">
         <v>46203</v>
       </c>
       <c r="H152" s="10">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="I152" s="10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="J152" s="5">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -11373,19 +11373,19 @@
         <v>41</v>
       </c>
       <c r="F153" s="10">
-        <v>26.05</v>
+        <v>21.29</v>
       </c>
       <c r="G153" s="9">
         <v>46203</v>
       </c>
       <c r="H153" s="10">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="I153" s="10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J153" s="5">
-        <v>27.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -11405,19 +11405,19 @@
         <v>41</v>
       </c>
       <c r="F154" s="10">
-        <v>16.24</v>
+        <v>16.15</v>
       </c>
       <c r="G154" s="9">
         <v>46203</v>
       </c>
       <c r="H154" s="10">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="I154" s="10">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="J154" s="5">
-        <v>17.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -11437,19 +11437,19 @@
         <v>41</v>
       </c>
       <c r="F155" s="10">
-        <v>28.3</v>
+        <v>31.52</v>
       </c>
       <c r="G155" s="9">
         <v>46203</v>
       </c>
       <c r="H155" s="10">
-        <v>2.74</v>
+        <v>1.69</v>
       </c>
       <c r="I155" s="10">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="J155" s="5">
-        <v>31</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -11469,19 +11469,19 @@
         <v>41</v>
       </c>
       <c r="F156" s="10">
-        <v>21.12</v>
+        <v>18.9</v>
       </c>
       <c r="G156" s="9">
         <v>46203</v>
       </c>
       <c r="H156" s="10">
-        <v>0.8</v>
+        <v>1.43</v>
       </c>
       <c r="I156" s="10">
         <v>0</v>
       </c>
       <c r="J156" s="5">
-        <v>21.9</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -11501,19 +11501,19 @@
         <v>41</v>
       </c>
       <c r="F157" s="10">
-        <v>21.48</v>
+        <v>20.15</v>
       </c>
       <c r="G157" s="9">
         <v>46203</v>
       </c>
       <c r="H157" s="10">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="I157" s="10">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="J157" s="5">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -11533,19 +11533,19 @@
         <v>41</v>
       </c>
       <c r="F158" s="10">
-        <v>32.08</v>
+        <v>22.43</v>
       </c>
       <c r="G158" s="9">
         <v>46203</v>
       </c>
       <c r="H158" s="10">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="I158" s="10">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J158" s="5">
-        <v>31.2</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -11565,19 +11565,19 @@
         <v>41</v>
       </c>
       <c r="F159" s="10">
-        <v>32.71</v>
+        <v>31.09</v>
       </c>
       <c r="G159" s="9">
         <v>46203</v>
       </c>
       <c r="H159" s="10">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="I159" s="10">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="J159" s="5">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -11597,19 +11597,19 @@
         <v>41</v>
       </c>
       <c r="F160" s="10">
-        <v>-0.48</v>
+        <v>1.91</v>
       </c>
       <c r="G160" s="9">
         <v>46203</v>
       </c>
       <c r="H160" s="10">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="I160" s="10">
         <v>0</v>
       </c>
       <c r="J160" s="5">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -11629,19 +11629,19 @@
         <v>41</v>
       </c>
       <c r="F161" s="10">
-        <v>12.71</v>
+        <v>10.22</v>
       </c>
       <c r="G161" s="9">
         <v>46203</v>
       </c>
       <c r="H161" s="10">
-        <v>5.16</v>
+        <v>9.93</v>
       </c>
       <c r="I161" s="10">
         <v>0</v>
       </c>
       <c r="J161" s="5">
-        <v>17.9</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -11661,19 +11661,19 @@
         <v>41</v>
       </c>
       <c r="F162" s="10">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="G162" s="9">
         <v>46203</v>
       </c>
       <c r="H162" s="10">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="I162" s="10">
         <v>0</v>
       </c>
       <c r="J162" s="5">
-        <v>0.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -11681,7 +11681,7 @@
         <v>21</v>
       </c>
       <c r="J163" s="11">
-        <v>1331.8</v>
+        <v>1411.2</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -11726,7 +11726,7 @@
         <v>356</v>
       </c>
       <c r="B5" s="5">
-        <v>210.6</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -11787,7 +11787,7 @@
         <v>364</v>
       </c>
       <c r="B14" s="5">
-        <v>400</v>
+        <v>350.4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -11827,7 +11827,7 @@
         <v>356</v>
       </c>
       <c r="B19" s="5">
-        <v>210.6</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
